--- a/Deliverables/Self Assessment Rubric - Y1B- 2024-25_ADSAI.xlsx
+++ b/Deliverables/Self Assessment Rubric - Y1B- 2024-25_ADSAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edubuas.sharepoint.com/teams/ADSAI24-25/Shared Documents/General/Design documentation/Year 1/Block B/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maksb\Documents\GitHub\2024-25b-fai1-adsai-MaksBurchard240894\Deliverables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92BD1742-A6B6-4178-B91E-06D1034FA622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB11FCF-8841-4AF7-93FD-49F60031DED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34800" yWindow="760" windowWidth="38400" windowHeight="21100" xr2:uid="{DAAEC50E-5317-F24F-8628-0EA25586FBC3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{DAAEC50E-5317-F24F-8628-0EA25586FBC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Self-Assessment_main" sheetId="5" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="ASSESSMENT RUBRIC" sheetId="2" state="hidden" r:id="rId5"/>
     <sheet name="Overview" sheetId="3" state="hidden" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="330">
   <si>
     <t>Details</t>
   </si>
@@ -95,16 +95,10 @@
     <t>Student Number</t>
   </si>
   <si>
-    <t>&lt;&lt;provide student number&gt;&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;&lt; fill in your self-assessment comments, any other academic feedback for the 8 weeks of work &gt;&gt; </t>
   </si>
   <si>
     <t>Student Name</t>
-  </si>
-  <si>
-    <t>&lt;&lt;fill student name&gt;&gt;</t>
   </si>
   <si>
     <t>Project</t>
@@ -257,6 +251,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+      </rPr>
       <t>Goals written with a</t>
     </r>
     <r>
@@ -551,6 +550,12 @@
     <t>Have the learning skills to allow them to continue to study in a manner that may be largely self-directed or autonomous.</t>
   </si>
   <si>
+    <t>&lt;&lt;provide student number&gt;&gt;</t>
+  </si>
+  <si>
+    <t>&lt;&lt;fill student name&gt;&gt;</t>
+  </si>
+  <si>
     <t>0.2 Students are able to demonstrate a advanced understanding of python programming concepts and basics of SQL.</t>
   </si>
   <si>
@@ -594,6 +599,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos"/>
+        <family val="2"/>
       </rPr>
       <t>Goals written with a</t>
     </r>
@@ -603,6 +609,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> SMARTER </t>
     </r>
@@ -611,6 +618,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos"/>
+        <family val="2"/>
       </rPr>
       <t>method. The goals are shown to be Specific, Measurable, Achievable, Relevant, Time-bound, Evaluated and Readjusted. Project goals and self-development goals detailed.</t>
     </r>
@@ -1124,12 +1132,18 @@
   <si>
     <t>Is aware of legal and ethical aspects within the context of her professional work environment and is able to make substantiated considerations in this regard. She acts from justice and integrity.</t>
   </si>
+  <si>
+    <t>Maks Burchard</t>
+  </si>
+  <si>
+    <t>240894</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="51">
+  <fonts count="50">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1372,28 +1386,20 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -1411,15 +1417,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1456,6 +1458,17 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="49">
@@ -2369,7 +2382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="281">
+  <cellXfs count="282">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2760,33 +2773,15 @@
     <xf numFmtId="0" fontId="1" fillId="44" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="45" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="45" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="45" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="45" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="40" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2821,8 +2816,8 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2842,100 +2837,176 @@
     <xf numFmtId="0" fontId="13" fillId="43" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="36" fillId="45" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="45" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="41" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="41" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="41" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="48" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="48" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="36" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="36" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="41" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="41" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="41" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2956,116 +3027,72 @@
     <xf numFmtId="0" fontId="36" fillId="38" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="41" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="48" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="48" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="36" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3076,18 +3103,16 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3097,6 +3122,10 @@
     <xf numFmtId="0" fontId="7" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3106,35 +3135,22 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="84">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3173,22 +3189,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E6FC"/>
-          <bgColor rgb="FFD9E6FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9F1F3"/>
-          <bgColor rgb="FFD9F1F3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3235,80 +3235,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD2F1DA"/>
-          <bgColor rgb="FFD2F1DA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF1CC"/>
-          <bgColor rgb="FFFEF1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE1CC"/>
-          <bgColor rgb="FFFEE1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAD9D6"/>
-          <bgColor rgb="FFFAD9D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFD9E6FC"/>
           <bgColor rgb="FFD9E6FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9F1F3"/>
-          <bgColor rgb="FFD9F1F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD2F1DA"/>
-          <bgColor rgb="FFD2F1DA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF1CC"/>
-          <bgColor rgb="FFFEF1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAD9D6"/>
-          <bgColor rgb="FFFAD9D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE1CC"/>
-          <bgColor rgb="FFFEE1CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3363,8 +3291,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9E6FC"/>
-          <bgColor rgb="FFD9E6FC"/>
+          <fgColor rgb="FFFAD9D6"/>
+          <bgColor rgb="FFFAD9D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3373,14 +3301,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFEE1CC"/>
           <bgColor rgb="FFFEE1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAD9D6"/>
-          <bgColor rgb="FFFAD9D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3413,242 +3333,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFD9E6FC"/>
           <bgColor rgb="FFD9E6FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E6FC"/>
-          <bgColor rgb="FFD9E6FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9F1F3"/>
-          <bgColor rgb="FFD9F1F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD2F1DA"/>
-          <bgColor rgb="FFD2F1DA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF1CC"/>
-          <bgColor rgb="FFFEF1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAD9D6"/>
-          <bgColor rgb="FFFAD9D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE1CC"/>
-          <bgColor rgb="FFFEE1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF63D297"/>
-          <bgColor rgb="FF63D297"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E6FC"/>
-          <bgColor rgb="FFD9E6FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9F1F3"/>
-          <bgColor rgb="FFD9F1F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD2F1DA"/>
-          <bgColor rgb="FFD2F1DA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF1CC"/>
-          <bgColor rgb="FFFEF1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAD9D6"/>
-          <bgColor rgb="FFFAD9D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE1CC"/>
-          <bgColor rgb="FFFEE1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9F1F3"/>
-          <bgColor rgb="FFD9F1F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD2F1DA"/>
-          <bgColor rgb="FFD2F1DA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF1CC"/>
-          <bgColor rgb="FFFEF1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE1CC"/>
-          <bgColor rgb="FFFEE1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAD9D6"/>
-          <bgColor rgb="FFFAD9D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E6FC"/>
-          <bgColor rgb="FFD9E6FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9F1F3"/>
-          <bgColor rgb="FFD9F1F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD2F1DA"/>
-          <bgColor rgb="FFD2F1DA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF1CC"/>
-          <bgColor rgb="FFFEF1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAD9D6"/>
-          <bgColor rgb="FFFAD9D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE1CC"/>
-          <bgColor rgb="FFFEE1CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3703,6 +3387,202 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFEE1CC"/>
+          <bgColor rgb="FFFEE1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF1CC"/>
+          <bgColor rgb="FFFEF1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD2F1DA"/>
+          <bgColor rgb="FFD2F1DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E6FC"/>
+          <bgColor rgb="FFD9E6FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAD9D6"/>
+          <bgColor rgb="FFFAD9D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAD9D6"/>
+          <bgColor rgb="FFFAD9D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE1CC"/>
+          <bgColor rgb="FFFEE1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E6FC"/>
+          <bgColor rgb="FFD9E6FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD2F1DA"/>
+          <bgColor rgb="FFD2F1DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF1CC"/>
+          <bgColor rgb="FFFEF1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF63D297"/>
+          <bgColor rgb="FF63D297"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD2F1DA"/>
+          <bgColor rgb="FFD2F1DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF1CC"/>
+          <bgColor rgb="FFFEF1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAD9D6"/>
+          <bgColor rgb="FFFAD9D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE1CC"/>
+          <bgColor rgb="FFFEE1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E6FC"/>
+          <bgColor rgb="FFD9E6FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFD9E6FC"/>
           <bgColor rgb="FFD9E6FC"/>
         </patternFill>
@@ -3751,8 +3631,160 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFAD9D6"/>
+          <bgColor rgb="FFFAD9D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE1CC"/>
+          <bgColor rgb="FFFEE1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF1CC"/>
+          <bgColor rgb="FFFEF1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD2F1DA"/>
+          <bgColor rgb="FFD2F1DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFD9E6FC"/>
           <bgColor rgb="FFD9E6FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E6FC"/>
+          <bgColor rgb="FFD9E6FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE1CC"/>
+          <bgColor rgb="FFFEE1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAD9D6"/>
+          <bgColor rgb="FFFAD9D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF1CC"/>
+          <bgColor rgb="FFFEF1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD2F1DA"/>
+          <bgColor rgb="FFD2F1DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE1CC"/>
+          <bgColor rgb="FFFEE1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF1CC"/>
+          <bgColor rgb="FFFEF1CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD2F1DA"/>
+          <bgColor rgb="FFD2F1DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F1F3"/>
+          <bgColor rgb="FFD9F1F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E6FC"/>
+          <bgColor rgb="FFD9E6FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAD9D6"/>
+          <bgColor rgb="FFFAD9D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAD9D6"/>
+          <bgColor rgb="FFFAD9D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE1CC"/>
+          <bgColor rgb="FFFEE1CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3785,22 +3817,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFEF1CC"/>
           <bgColor rgb="FFFEF1CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAD9D6"/>
-          <bgColor rgb="FFFAD9D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE1CC"/>
-          <bgColor rgb="FFFEE1CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4030,26 +4046,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y1019"/>
-  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="45" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" style="45" customWidth="1"/>
+    <col min="1" max="2" width="9.1796875" style="45" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" style="45" customWidth="1"/>
     <col min="4" max="4" width="27" style="45" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="45" customWidth="1"/>
-    <col min="6" max="6" width="37.85546875" style="45" customWidth="1"/>
-    <col min="7" max="7" width="29.28515625" style="45" customWidth="1"/>
-    <col min="8" max="8" width="29.7109375" style="45" customWidth="1"/>
-    <col min="9" max="9" width="33.140625" style="45" customWidth="1"/>
-    <col min="10" max="11" width="36.7109375" style="45" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" style="45" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" style="45" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" style="45" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" style="45" customWidth="1"/>
-    <col min="16" max="25" width="14.42578125" style="45" customWidth="1"/>
-    <col min="26" max="16384" width="12.42578125" style="45"/>
+    <col min="5" max="5" width="22.7265625" style="45" customWidth="1"/>
+    <col min="6" max="6" width="37.81640625" style="45" customWidth="1"/>
+    <col min="7" max="7" width="29.26953125" style="45" customWidth="1"/>
+    <col min="8" max="8" width="29.7265625" style="45" customWidth="1"/>
+    <col min="9" max="9" width="33.1796875" style="45" customWidth="1"/>
+    <col min="10" max="11" width="36.7265625" style="45" customWidth="1"/>
+    <col min="12" max="12" width="17.1796875" style="45" customWidth="1"/>
+    <col min="13" max="13" width="6.7265625" style="45" customWidth="1"/>
+    <col min="14" max="14" width="17.1796875" style="45" customWidth="1"/>
+    <col min="15" max="15" width="6.7265625" style="45" customWidth="1"/>
+    <col min="16" max="25" width="14.453125" style="45" customWidth="1"/>
+    <col min="26" max="16384" width="12.453125" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A1" s="80"/>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -4066,22 +4082,22 @@
       <c r="N1" s="80"/>
       <c r="O1" s="80"/>
     </row>
-    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A2" s="80"/>
       <c r="B2" s="47"/>
-      <c r="C2" s="249"/>
-      <c r="D2" s="268"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="185"/>
       <c r="E2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="250" t="s">
+      <c r="F2" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="250"/>
-      <c r="J2" s="250"/>
-      <c r="K2" s="250"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="186"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="186"/>
       <c r="L2" s="66" t="s">
         <v>2</v>
       </c>
@@ -4101,117 +4117,117 @@
       <c r="X2" s="48"/>
       <c r="Y2" s="48"/>
     </row>
-    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="3" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A3" s="80"/>
       <c r="B3" s="49"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="246"/>
+      <c r="D3" s="188"/>
       <c r="E3" s="61" t="s">
+        <v>329</v>
+      </c>
+      <c r="F3" s="189" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="251" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="252"/>
-      <c r="H3" s="252"/>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="254">
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="190"/>
+      <c r="J3" s="190"/>
+      <c r="K3" s="191"/>
+      <c r="L3" s="192">
         <v>0</v>
       </c>
-      <c r="M3" s="248"/>
-      <c r="N3" s="242" t="str">
+      <c r="M3" s="202"/>
+      <c r="N3" s="198" t="str">
         <f>IF(L3&gt;=5.5,"PASS",IF(L3&gt;0,"FAIL","M/O"))</f>
         <v>M/O</v>
       </c>
       <c r="O3" s="80"/>
     </row>
-    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A4" s="80"/>
       <c r="B4" s="49"/>
-      <c r="C4" s="245" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="246"/>
+      <c r="C4" s="187" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="188"/>
       <c r="E4" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="251"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="253"/>
-      <c r="L4" s="269"/>
-      <c r="M4" s="270"/>
-      <c r="N4" s="243"/>
+        <v>328</v>
+      </c>
+      <c r="F4" s="189"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="190"/>
+      <c r="K4" s="191"/>
+      <c r="L4" s="193"/>
+      <c r="M4" s="203"/>
+      <c r="N4" s="199"/>
       <c r="O4" s="80"/>
     </row>
-    <row r="5" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A5" s="80"/>
       <c r="B5" s="49"/>
-      <c r="C5" s="245" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="246"/>
+      <c r="C5" s="187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="188"/>
       <c r="E5" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="251"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="253"/>
-      <c r="L5" s="269"/>
-      <c r="M5" s="270"/>
-      <c r="N5" s="243"/>
+        <v>8</v>
+      </c>
+      <c r="F5" s="189"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="190"/>
+      <c r="J5" s="190"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="193"/>
+      <c r="M5" s="203"/>
+      <c r="N5" s="199"/>
       <c r="O5" s="80"/>
     </row>
-    <row r="6" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A6" s="80"/>
       <c r="B6" s="49"/>
-      <c r="C6" s="245" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="246"/>
+      <c r="C6" s="187" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="188"/>
       <c r="E6" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="251"/>
-      <c r="G6" s="252"/>
-      <c r="H6" s="252"/>
-      <c r="I6" s="252"/>
-      <c r="J6" s="252"/>
-      <c r="K6" s="253"/>
-      <c r="L6" s="269"/>
-      <c r="M6" s="270"/>
-      <c r="N6" s="243"/>
+        <v>10</v>
+      </c>
+      <c r="F6" s="189"/>
+      <c r="G6" s="190"/>
+      <c r="H6" s="190"/>
+      <c r="I6" s="190"/>
+      <c r="J6" s="190"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="193"/>
+      <c r="M6" s="203"/>
+      <c r="N6" s="199"/>
       <c r="O6" s="80"/>
     </row>
-    <row r="7" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A7" s="80"/>
       <c r="B7" s="49"/>
-      <c r="C7" s="245" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="246"/>
+      <c r="C7" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="188"/>
       <c r="E7" s="60"/>
-      <c r="F7" s="251"/>
-      <c r="G7" s="252"/>
-      <c r="H7" s="252"/>
-      <c r="I7" s="252"/>
-      <c r="J7" s="252"/>
-      <c r="K7" s="253"/>
-      <c r="L7" s="269"/>
-      <c r="M7" s="270"/>
-      <c r="N7" s="244"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="191"/>
+      <c r="L7" s="193"/>
+      <c r="M7" s="203"/>
+      <c r="N7" s="200"/>
       <c r="O7" s="80"/>
     </row>
-    <row r="8" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A8" s="80"/>
       <c r="B8" s="46"/>
       <c r="C8" s="46"/>
@@ -4245,22 +4261,22 @@
       <c r="N9" s="80"/>
       <c r="O9" s="80"/>
     </row>
-    <row r="10" spans="1:25" ht="24.95" customHeight="1">
+    <row r="10" spans="1:25" ht="25" customHeight="1">
       <c r="A10" s="80"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="247" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="247"/>
-      <c r="E10" s="247"/>
-      <c r="F10" s="247"/>
-      <c r="G10" s="247"/>
-      <c r="H10" s="247"/>
-      <c r="I10" s="247"/>
-      <c r="J10" s="247"/>
-      <c r="K10" s="247"/>
-      <c r="L10" s="247"/>
-      <c r="M10" s="247"/>
+      <c r="C10" s="201" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="201"/>
+      <c r="E10" s="201"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="201"/>
+      <c r="H10" s="201"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="201"/>
+      <c r="K10" s="201"/>
+      <c r="L10" s="201"/>
+      <c r="M10" s="201"/>
       <c r="N10" s="46"/>
       <c r="O10" s="80"/>
     </row>
@@ -4269,27 +4285,27 @@
       <c r="B11" s="46"/>
       <c r="C11" s="50"/>
       <c r="D11" s="51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E11" s="52"/>
       <c r="F11" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="205" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="205"/>
+      <c r="I11" s="205"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="205"/>
+      <c r="L11" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="228" t="s">
+      <c r="M11" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="228"/>
-      <c r="I11" s="228"/>
-      <c r="J11" s="228"/>
-      <c r="K11" s="228"/>
-      <c r="L11" s="50" t="s">
+      <c r="N11" s="50" t="s">
         <v>18</v>
-      </c>
-      <c r="M11" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" s="50" t="s">
-        <v>20</v>
       </c>
       <c r="O11" s="80"/>
     </row>
@@ -4314,48 +4330,48 @@
       <c r="A13" s="80"/>
       <c r="B13" s="46"/>
       <c r="C13" s="118" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="229" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="230"/>
-      <c r="F13" s="230"/>
-      <c r="G13" s="230"/>
-      <c r="H13" s="230"/>
-      <c r="I13" s="230"/>
-      <c r="J13" s="230"/>
-      <c r="K13" s="230"/>
+        <v>19</v>
+      </c>
+      <c r="D13" s="206" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="207"/>
+      <c r="F13" s="207"/>
+      <c r="G13" s="207"/>
+      <c r="H13" s="207"/>
+      <c r="I13" s="207"/>
+      <c r="J13" s="207"/>
+      <c r="K13" s="207"/>
       <c r="L13" s="53"/>
       <c r="M13" s="53"/>
       <c r="N13" s="54"/>
       <c r="O13" s="80"/>
     </row>
-    <row r="14" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A14" s="80"/>
       <c r="B14" s="46"/>
       <c r="C14" s="118"/>
-      <c r="D14" s="231"/>
-      <c r="E14" s="232"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="209"/>
       <c r="F14" s="139" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="143" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="143" t="s">
+      <c r="I14" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="143" t="s">
+      <c r="J14" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="143" t="s">
+      <c r="K14" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="143" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" s="167"/>
+      <c r="L14" s="159"/>
       <c r="M14" s="121"/>
       <c r="N14" s="122"/>
       <c r="O14" s="80"/>
@@ -4365,66 +4381,66 @@
       <c r="B15" s="46"/>
       <c r="C15" s="113"/>
       <c r="D15" s="210" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="211"/>
+      <c r="F15" s="152" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="162" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="203"/>
-      <c r="F15" s="160" t="s">
+      <c r="H15" s="162" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="170" t="s">
+      <c r="I15" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="170" t="s">
+      <c r="J15" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="170" t="s">
+      <c r="K15" s="162" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="170" t="s">
+      <c r="L15" s="154">
+        <v>9</v>
+      </c>
+      <c r="M15" s="194" t="s">
         <v>34</v>
-      </c>
-      <c r="K15" s="170" t="s">
-        <v>35</v>
-      </c>
-      <c r="L15" s="162">
-        <v>0</v>
-      </c>
-      <c r="M15" s="239" t="s">
-        <v>36</v>
       </c>
       <c r="N15" s="126">
         <v>15</v>
       </c>
       <c r="O15" s="80"/>
     </row>
-    <row r="16" spans="1:25" ht="24.95" customHeight="1">
+    <row r="16" spans="1:25" ht="25" customHeight="1">
       <c r="A16" s="80"/>
       <c r="B16" s="46"/>
       <c r="C16" s="112"/>
-      <c r="D16" s="241" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="204"/>
+      <c r="D16" s="196" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="197"/>
       <c r="F16" s="140" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G16" s="144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="144">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" s="144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="144">
-        <v>0</v>
-      </c>
-      <c r="L16" s="168"/>
-      <c r="M16" s="240"/>
+        <v>1</v>
+      </c>
+      <c r="L16" s="160"/>
+      <c r="M16" s="195"/>
       <c r="N16" s="127"/>
       <c r="O16" s="80"/>
     </row>
@@ -4432,48 +4448,48 @@
       <c r="A17" s="80"/>
       <c r="B17" s="46"/>
       <c r="C17" s="118" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="196" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="196"/>
-      <c r="F17" s="196"/>
-      <c r="G17" s="196"/>
-      <c r="H17" s="196"/>
-      <c r="I17" s="196"/>
-      <c r="J17" s="196"/>
-      <c r="K17" s="196"/>
+        <v>37</v>
+      </c>
+      <c r="D17" s="212" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="212"/>
+      <c r="F17" s="212"/>
+      <c r="G17" s="212"/>
+      <c r="H17" s="212"/>
+      <c r="I17" s="212"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="212"/>
       <c r="L17" s="77"/>
       <c r="M17" s="78"/>
       <c r="N17" s="79"/>
       <c r="O17" s="80"/>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A18" s="80"/>
       <c r="B18" s="46"/>
       <c r="C18" s="118"/>
-      <c r="D18" s="231"/>
-      <c r="E18" s="232"/>
+      <c r="D18" s="208"/>
+      <c r="E18" s="209"/>
       <c r="F18" s="139" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G18" s="143" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="143" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="143" t="s">
+      <c r="J18" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="I18" s="143" t="s">
+      <c r="K18" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="J18" s="143" t="s">
-        <v>44</v>
-      </c>
-      <c r="K18" s="143" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18" s="161"/>
+      <c r="L18" s="153"/>
       <c r="M18" s="124"/>
       <c r="N18" s="125"/>
       <c r="O18" s="80"/>
@@ -4483,64 +4499,64 @@
       <c r="B19" s="46"/>
       <c r="C19" s="113"/>
       <c r="D19" s="210" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="211"/>
+      <c r="F19" s="135" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="167" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="203"/>
-      <c r="F19" s="135" t="s">
+      <c r="H19" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="175" t="s">
+      <c r="I19" s="141" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="164" t="s">
+      <c r="J19" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="141" t="s">
+      <c r="K19" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="141" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="179" t="s">
-        <v>52</v>
-      </c>
-      <c r="L19" s="162">
+      <c r="L19" s="154">
         <f>IF(F20="Yes",SUM(G20:K20)*2,0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M19" s="124" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N19" s="125">
         <v>10</v>
       </c>
       <c r="O19" s="80"/>
     </row>
-    <row r="20" spans="1:25" ht="24.95" customHeight="1">
+    <row r="20" spans="1:25" ht="25" customHeight="1">
       <c r="A20" s="80"/>
       <c r="B20" s="46"/>
       <c r="C20" s="112"/>
-      <c r="D20" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="205"/>
+      <c r="D20" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="213"/>
       <c r="F20" s="140" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G20" s="144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="144">
-        <v>0</v>
-      </c>
-      <c r="I20" s="163">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I20" s="155">
+        <v>2</v>
       </c>
       <c r="J20" s="144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" s="144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="77"/>
       <c r="M20" s="78"/>
@@ -4560,18 +4576,18 @@
       <c r="A21" s="80"/>
       <c r="B21" s="46"/>
       <c r="C21" s="118" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="233" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="271"/>
-      <c r="F21" s="271"/>
-      <c r="G21" s="271"/>
-      <c r="H21" s="271"/>
-      <c r="I21" s="271"/>
-      <c r="J21" s="271"/>
-      <c r="K21" s="271"/>
+        <v>51</v>
+      </c>
+      <c r="D21" s="214" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="215"/>
+      <c r="F21" s="215"/>
+      <c r="G21" s="215"/>
+      <c r="H21" s="215"/>
+      <c r="I21" s="215"/>
+      <c r="J21" s="215"/>
+      <c r="K21" s="215"/>
       <c r="L21" s="123"/>
       <c r="M21" s="124"/>
       <c r="N21" s="125"/>
@@ -4586,24 +4602,24 @@
       <c r="X21"/>
       <c r="Y21"/>
     </row>
-    <row r="22" spans="1:25" ht="24.95" customHeight="1">
+    <row r="22" spans="1:25" ht="25" customHeight="1">
       <c r="A22" s="80"/>
       <c r="B22" s="46"/>
       <c r="C22" s="118"/>
-      <c r="D22" s="207"/>
-      <c r="E22" s="207"/>
+      <c r="D22" s="204"/>
+      <c r="E22" s="204"/>
       <c r="F22" s="139" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="234" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="235"/>
-      <c r="I22" s="236"/>
-      <c r="J22" s="237" t="s">
-        <v>56</v>
-      </c>
-      <c r="K22" s="238"/>
+        <v>21</v>
+      </c>
+      <c r="G22" s="216" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="217"/>
+      <c r="I22" s="218"/>
+      <c r="J22" s="219" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="220"/>
       <c r="L22" s="123"/>
       <c r="M22" s="124"/>
       <c r="N22" s="125"/>
@@ -4623,27 +4639,27 @@
       <c r="B23" s="46"/>
       <c r="C23" s="112"/>
       <c r="D23" s="210" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="211"/>
+      <c r="F23" s="135" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="255" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="225"/>
+      <c r="I23" s="256"/>
+      <c r="J23" s="224" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="203"/>
-      <c r="F23" s="135" t="s">
-        <v>47</v>
-      </c>
-      <c r="G23" s="188" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="189"/>
-      <c r="I23" s="190"/>
-      <c r="J23" s="188" t="s">
-        <v>59</v>
-      </c>
-      <c r="K23" s="189"/>
+      <c r="K23" s="225"/>
       <c r="L23" s="123">
         <f>IF(F24="Yes",SUM(G24:K24),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" s="124" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N23" s="125">
         <v>10</v>
@@ -4659,26 +4675,26 @@
       <c r="X23"/>
       <c r="Y23"/>
     </row>
-    <row r="24" spans="1:25" ht="24.95" customHeight="1">
+    <row r="24" spans="1:25" ht="25" customHeight="1">
       <c r="A24" s="80"/>
       <c r="B24" s="46"/>
       <c r="C24" s="112"/>
-      <c r="D24" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="205"/>
+      <c r="D24" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="213"/>
       <c r="F24" s="140" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="223">
-        <v>0</v>
-      </c>
-      <c r="H24" s="224"/>
-      <c r="I24" s="225"/>
-      <c r="J24" s="226">
-        <v>0</v>
-      </c>
-      <c r="K24" s="227"/>
+        <v>36</v>
+      </c>
+      <c r="G24" s="228">
+        <v>5</v>
+      </c>
+      <c r="H24" s="229"/>
+      <c r="I24" s="230"/>
+      <c r="J24" s="231">
+        <v>3</v>
+      </c>
+      <c r="K24" s="232"/>
       <c r="L24" s="123"/>
       <c r="M24" s="124"/>
       <c r="N24" s="125"/>
@@ -4697,20 +4713,20 @@
       <c r="A25" s="80"/>
       <c r="B25" s="46"/>
       <c r="C25" s="118" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="221" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="222"/>
-      <c r="F25" s="222"/>
-      <c r="G25" s="222"/>
-      <c r="H25" s="222"/>
-      <c r="I25" s="222"/>
-      <c r="J25" s="222"/>
-      <c r="K25" s="222"/>
-      <c r="L25" s="222"/>
-      <c r="M25" s="222"/>
+        <v>58</v>
+      </c>
+      <c r="D25" s="226" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="227"/>
+      <c r="F25" s="227"/>
+      <c r="G25" s="227"/>
+      <c r="H25" s="227"/>
+      <c r="I25" s="227"/>
+      <c r="J25" s="227"/>
+      <c r="K25" s="227"/>
+      <c r="L25" s="227"/>
+      <c r="M25" s="227"/>
       <c r="N25" s="68"/>
       <c r="O25" s="80"/>
       <c r="Q25"/>
@@ -4723,24 +4739,24 @@
       <c r="X25"/>
       <c r="Y25"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A26" s="80"/>
       <c r="B26" s="46"/>
       <c r="C26" s="118"/>
-      <c r="D26" s="207"/>
-      <c r="E26" s="207"/>
+      <c r="D26" s="204"/>
+      <c r="E26" s="204"/>
       <c r="F26" s="120" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="218" t="s">
-        <v>55</v>
-      </c>
-      <c r="H26" s="219"/>
-      <c r="I26" s="220"/>
-      <c r="J26" s="218" t="s">
-        <v>56</v>
-      </c>
-      <c r="K26" s="220"/>
+        <v>21</v>
+      </c>
+      <c r="G26" s="221" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="222"/>
+      <c r="I26" s="223"/>
+      <c r="J26" s="221" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" s="223"/>
       <c r="L26" s="73"/>
       <c r="M26" s="76"/>
       <c r="N26" s="71"/>
@@ -4760,27 +4776,27 @@
       <c r="B27" s="46"/>
       <c r="C27" s="112"/>
       <c r="D27" s="210" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="211"/>
+      <c r="F27" s="152" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="233" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" s="234"/>
+      <c r="I27" s="235"/>
+      <c r="J27" s="233" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="203"/>
-      <c r="F27" s="160" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="211" t="s">
-        <v>63</v>
-      </c>
-      <c r="H27" s="212"/>
-      <c r="I27" s="213"/>
-      <c r="J27" s="211" t="s">
-        <v>64</v>
-      </c>
-      <c r="K27" s="212"/>
+      <c r="K27" s="235"/>
       <c r="L27" s="123">
         <f>IF(F28="Yes",SUM(G28:K28),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M27" s="128" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N27" s="122">
         <v>10</v>
@@ -4796,26 +4812,26 @@
       <c r="X27"/>
       <c r="Y27"/>
     </row>
-    <row r="28" spans="1:25" ht="24.95" customHeight="1">
+    <row r="28" spans="1:25" ht="25" customHeight="1">
       <c r="A28" s="80"/>
       <c r="B28" s="46"/>
       <c r="C28" s="112"/>
-      <c r="D28" s="214" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="204"/>
+      <c r="D28" s="236" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="197"/>
       <c r="F28" s="132" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="215">
-        <v>0</v>
-      </c>
-      <c r="H28" s="216"/>
-      <c r="I28" s="217"/>
-      <c r="J28" s="215">
-        <v>0</v>
-      </c>
-      <c r="K28" s="217"/>
+        <v>36</v>
+      </c>
+      <c r="G28" s="237">
+        <v>5</v>
+      </c>
+      <c r="H28" s="238"/>
+      <c r="I28" s="239"/>
+      <c r="J28" s="237">
+        <v>5</v>
+      </c>
+      <c r="K28" s="239"/>
       <c r="L28" s="129"/>
       <c r="M28" s="130"/>
       <c r="N28" s="131"/>
@@ -4834,18 +4850,18 @@
       <c r="A29" s="80"/>
       <c r="B29" s="46"/>
       <c r="C29" s="118" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="196" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="271"/>
-      <c r="F29" s="271"/>
-      <c r="G29" s="271"/>
-      <c r="H29" s="271"/>
-      <c r="I29" s="271"/>
-      <c r="J29" s="271"/>
-      <c r="K29" s="271"/>
+        <v>63</v>
+      </c>
+      <c r="D29" s="212" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="215"/>
+      <c r="F29" s="215"/>
+      <c r="G29" s="215"/>
+      <c r="H29" s="215"/>
+      <c r="I29" s="215"/>
+      <c r="J29" s="215"/>
+      <c r="K29" s="215"/>
       <c r="L29" s="74"/>
       <c r="M29" s="69"/>
       <c r="N29" s="72"/>
@@ -4860,29 +4876,29 @@
       <c r="X29"/>
       <c r="Y29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A30" s="80"/>
       <c r="B30" s="46"/>
       <c r="C30" s="118"/>
-      <c r="D30" s="207"/>
-      <c r="E30" s="207"/>
+      <c r="D30" s="204"/>
+      <c r="E30" s="204"/>
       <c r="F30" s="120" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="H30" s="120" t="s">
+        <v>66</v>
+      </c>
+      <c r="I30" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="H30" s="120" t="s">
+      <c r="J30" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="I30" s="120" t="s">
+      <c r="K30" s="120" t="s">
         <v>69</v>
-      </c>
-      <c r="J30" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="K30" s="120" t="s">
-        <v>71</v>
       </c>
       <c r="L30" s="73"/>
       <c r="M30" s="76"/>
@@ -4902,34 +4918,34 @@
       <c r="A31" s="80"/>
       <c r="B31" s="46"/>
       <c r="C31" s="112"/>
-      <c r="D31" s="208" t="s">
+      <c r="D31" s="240" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="241"/>
+      <c r="F31" s="135" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="E31" s="209"/>
-      <c r="F31" s="135" t="s">
+      <c r="H31" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="G31" s="136" t="s">
+      <c r="I31" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="H31" s="136" t="s">
+      <c r="J31" s="136" t="s">
         <v>75</v>
       </c>
-      <c r="I31" s="137" t="s">
+      <c r="K31" s="138" t="s">
         <v>76</v>
-      </c>
-      <c r="J31" s="136" t="s">
-        <v>77</v>
-      </c>
-      <c r="K31" s="138" t="s">
-        <v>78</v>
       </c>
       <c r="L31" s="123">
         <f>IF(F32="Yes",SUM(G32:K32),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M31" s="128" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N31" s="122">
         <v>20</v>
@@ -4945,31 +4961,31 @@
       <c r="X31"/>
       <c r="Y31"/>
     </row>
-    <row r="32" spans="1:25" ht="24.95" customHeight="1">
+    <row r="32" spans="1:25" ht="25" customHeight="1">
       <c r="A32" s="80"/>
       <c r="B32" s="46"/>
       <c r="C32" s="112"/>
-      <c r="D32" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="205"/>
+      <c r="D32" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="213"/>
       <c r="F32" s="132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G32" s="134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" s="134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" s="134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" s="133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="123"/>
       <c r="M32" s="128"/>
@@ -4989,18 +5005,18 @@
       <c r="A33" s="80"/>
       <c r="B33" s="46"/>
       <c r="C33" s="118" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="196" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="271"/>
-      <c r="F33" s="271"/>
-      <c r="G33" s="271"/>
-      <c r="H33" s="271"/>
-      <c r="I33" s="271"/>
-      <c r="J33" s="271"/>
-      <c r="K33" s="271"/>
+        <v>63</v>
+      </c>
+      <c r="D33" s="212" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="215"/>
+      <c r="F33" s="215"/>
+      <c r="G33" s="215"/>
+      <c r="H33" s="215"/>
+      <c r="I33" s="215"/>
+      <c r="J33" s="215"/>
+      <c r="K33" s="215"/>
       <c r="L33" s="74"/>
       <c r="M33" s="69"/>
       <c r="N33" s="72"/>
@@ -5015,29 +5031,29 @@
       <c r="X33"/>
       <c r="Y33"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="34" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A34" s="80"/>
       <c r="B34" s="46"/>
       <c r="C34" s="118"/>
-      <c r="D34" s="207"/>
-      <c r="E34" s="207"/>
+      <c r="D34" s="204"/>
+      <c r="E34" s="204"/>
       <c r="F34" s="120" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G34" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" s="120" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="H34" s="120" t="s">
+      <c r="J34" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="I34" s="120" t="s">
+      <c r="K34" s="120" t="s">
         <v>69</v>
-      </c>
-      <c r="J34" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="K34" s="120" t="s">
-        <v>71</v>
       </c>
       <c r="L34" s="67"/>
       <c r="M34" s="69"/>
@@ -5057,34 +5073,34 @@
       <c r="A35" s="80"/>
       <c r="B35" s="55"/>
       <c r="C35" s="112"/>
-      <c r="D35" s="202" t="s">
+      <c r="D35" s="245" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="211"/>
+      <c r="F35" s="152" t="s">
+        <v>78</v>
+      </c>
+      <c r="G35" s="156" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="203"/>
-      <c r="F35" s="160" t="s">
+      <c r="H35" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="G35" s="164" t="s">
+      <c r="I35" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="H35" s="164" t="s">
+      <c r="J35" s="156" t="s">
         <v>82</v>
       </c>
-      <c r="I35" s="164" t="s">
+      <c r="K35" s="156" t="s">
         <v>83</v>
-      </c>
-      <c r="J35" s="164" t="s">
-        <v>84</v>
-      </c>
-      <c r="K35" s="164" t="s">
-        <v>85</v>
       </c>
       <c r="L35" s="67">
         <f>IF(F36="Yes",SUM(G36:K36),0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M35" s="75" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N35" s="68">
         <v>20</v>
@@ -5101,31 +5117,31 @@
       <c r="X35"/>
       <c r="Y35"/>
     </row>
-    <row r="36" spans="1:25" ht="24.95" customHeight="1">
+    <row r="36" spans="1:25" ht="25" customHeight="1">
       <c r="A36" s="80"/>
       <c r="B36" s="55"/>
       <c r="C36" s="112"/>
-      <c r="D36" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" s="205"/>
+      <c r="D36" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="213"/>
       <c r="F36" s="132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G36" s="134">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" s="134">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I36" s="134">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J36" s="134">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K36" s="133">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L36" s="67"/>
       <c r="M36" s="69"/>
@@ -5146,18 +5162,18 @@
       <c r="A37" s="80"/>
       <c r="B37" s="55"/>
       <c r="C37" s="118" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="206" t="s">
-        <v>87</v>
-      </c>
-      <c r="E37" s="271"/>
-      <c r="F37" s="271"/>
-      <c r="G37" s="271"/>
-      <c r="H37" s="271"/>
-      <c r="I37" s="271"/>
-      <c r="J37" s="271"/>
-      <c r="K37" s="271"/>
+        <v>84</v>
+      </c>
+      <c r="D37" s="246" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="215"/>
+      <c r="F37" s="215"/>
+      <c r="G37" s="215"/>
+      <c r="H37" s="215"/>
+      <c r="I37" s="215"/>
+      <c r="J37" s="215"/>
+      <c r="K37" s="215"/>
       <c r="L37" s="67"/>
       <c r="M37" s="69"/>
       <c r="N37" s="68"/>
@@ -5173,40 +5189,40 @@
       <c r="X37"/>
       <c r="Y37"/>
     </row>
-    <row r="38" spans="1:25" ht="24.95" customHeight="1">
+    <row r="38" spans="1:25" ht="25" customHeight="1">
       <c r="A38" s="80"/>
       <c r="B38" s="55"/>
       <c r="C38" s="118"/>
-      <c r="D38" s="207"/>
-      <c r="E38" s="207"/>
+      <c r="D38" s="204"/>
+      <c r="E38" s="204"/>
       <c r="F38" s="120" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="120" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="G38" s="120" t="s">
+      <c r="I38" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="120" t="s">
+      <c r="J38" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="I38" s="120" t="s">
+      <c r="K38" s="120" t="s">
         <v>26</v>
-      </c>
-      <c r="J38" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="K38" s="120" t="s">
-        <v>28</v>
       </c>
       <c r="L38" s="67"/>
       <c r="M38" s="69"/>
       <c r="N38" s="68"/>
       <c r="O38" s="80"/>
       <c r="P38" s="56"/>
-      <c r="Q38" s="176"/>
+      <c r="Q38" s="168"/>
       <c r="R38"/>
-      <c r="S38" s="176"/>
+      <c r="S38" s="168"/>
       <c r="T38"/>
-      <c r="U38" s="176"/>
+      <c r="U38" s="168"/>
       <c r="V38"/>
       <c r="W38"/>
       <c r="X38"/>
@@ -5216,60 +5232,60 @@
       <c r="A39" s="80"/>
       <c r="B39" s="57"/>
       <c r="C39" s="112"/>
-      <c r="D39" s="208" t="s">
+      <c r="D39" s="240" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" s="240"/>
+      <c r="F39" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="208"/>
-      <c r="F39" s="135" t="s">
+      <c r="H39" s="157" t="s">
         <v>89</v>
       </c>
-      <c r="G39" s="137" t="s">
+      <c r="I39" s="157" t="s">
         <v>90</v>
       </c>
-      <c r="H39" s="165" t="s">
+      <c r="J39" s="157" t="s">
         <v>91</v>
       </c>
-      <c r="I39" s="165" t="s">
+      <c r="K39" s="138" t="s">
         <v>92</v>
-      </c>
-      <c r="J39" s="165" t="s">
-        <v>93</v>
-      </c>
-      <c r="K39" s="138" t="s">
-        <v>94</v>
       </c>
       <c r="L39" s="67">
         <f>IF(F40="Yes",SUM(G40:K40),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="70" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N39" s="68">
         <v>15</v>
       </c>
       <c r="O39" s="80"/>
-      <c r="P39" s="177"/>
-      <c r="Q39" s="169"/>
-      <c r="R39" s="176"/>
-      <c r="S39" s="178"/>
-      <c r="T39" s="176"/>
-      <c r="U39" s="178"/>
-      <c r="V39" s="176"/>
+      <c r="P39" s="169"/>
+      <c r="Q39" s="161"/>
+      <c r="R39" s="168"/>
+      <c r="S39" s="170"/>
+      <c r="T39" s="168"/>
+      <c r="U39" s="170"/>
+      <c r="V39" s="168"/>
       <c r="W39"/>
       <c r="X39"/>
       <c r="Y39"/>
     </row>
-    <row r="40" spans="1:25" ht="24.95" customHeight="1">
+    <row r="40" spans="1:25" ht="25" customHeight="1">
       <c r="A40" s="80"/>
       <c r="B40" s="57"/>
       <c r="C40" s="112"/>
-      <c r="D40" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="205"/>
+      <c r="D40" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="213"/>
       <c r="F40" s="132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G40" s="134">
         <v>0</v>
@@ -5291,17 +5307,17 @@
       <c r="N40" s="68"/>
       <c r="O40" s="80"/>
       <c r="P40" s="58"/>
-      <c r="Q40" s="176"/>
+      <c r="Q40" s="168"/>
       <c r="R40"/>
-      <c r="S40" s="176"/>
+      <c r="S40" s="168"/>
       <c r="T40"/>
-      <c r="U40" s="176"/>
+      <c r="U40" s="168"/>
       <c r="V40"/>
       <c r="W40"/>
       <c r="X40"/>
       <c r="Y40"/>
     </row>
-    <row r="41" spans="1:25" ht="24.95" customHeight="1">
+    <row r="41" spans="1:25" ht="25" customHeight="1">
       <c r="A41" s="80"/>
       <c r="B41" s="59"/>
       <c r="D41" s="64"/>
@@ -5311,17 +5327,17 @@
       <c r="H41" s="65"/>
       <c r="I41" s="65"/>
       <c r="J41" s="65"/>
-      <c r="K41" s="192" t="s">
-        <v>95</v>
-      </c>
-      <c r="L41" s="193">
+      <c r="K41" s="257" t="s">
+        <v>93</v>
+      </c>
+      <c r="L41" s="258">
         <f>SUM(L15:L40)</f>
-        <v>0</v>
-      </c>
-      <c r="M41" s="194" t="s">
-        <v>36</v>
-      </c>
-      <c r="N41" s="200">
+        <v>75</v>
+      </c>
+      <c r="M41" s="259" t="s">
+        <v>34</v>
+      </c>
+      <c r="N41" s="242">
         <f>SUM(N15:N40)</f>
         <v>100</v>
       </c>
@@ -5336,7 +5352,7 @@
       <c r="X41"/>
       <c r="Y41"/>
     </row>
-    <row r="42" spans="1:25" ht="24.95" customHeight="1">
+    <row r="42" spans="1:25" ht="25" customHeight="1">
       <c r="A42" s="80"/>
       <c r="B42" s="59"/>
       <c r="D42" s="64"/>
@@ -5346,10 +5362,10 @@
       <c r="H42" s="65"/>
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
-      <c r="K42" s="192"/>
-      <c r="L42" s="193"/>
-      <c r="M42" s="195"/>
-      <c r="N42" s="200"/>
+      <c r="K42" s="257"/>
+      <c r="L42" s="258"/>
+      <c r="M42" s="260"/>
+      <c r="N42" s="242"/>
       <c r="O42" s="80"/>
       <c r="Q42"/>
       <c r="R42"/>
@@ -5381,11 +5397,11 @@
     <row r="44" spans="1:25" ht="30.75" customHeight="1">
       <c r="A44" s="80"/>
       <c r="B44" s="114"/>
-      <c r="C44" s="272" t="s">
-        <v>96</v>
-      </c>
-      <c r="D44" s="272"/>
-      <c r="E44" s="272"/>
+      <c r="C44" s="243" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="243"/>
+      <c r="E44" s="243"/>
       <c r="F44" s="81"/>
       <c r="G44" s="81"/>
       <c r="H44" s="81"/>
@@ -5401,23 +5417,23 @@
       <c r="A45" s="80"/>
       <c r="B45" s="104"/>
       <c r="C45" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="84" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="244" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="84" t="s">
-        <v>98</v>
-      </c>
-      <c r="E45" s="201" t="s">
-        <v>99</v>
-      </c>
-      <c r="F45" s="201"/>
-      <c r="G45" s="201"/>
-      <c r="H45" s="201"/>
-      <c r="I45" s="201"/>
+      <c r="F45" s="244"/>
+      <c r="G45" s="244"/>
+      <c r="H45" s="244"/>
+      <c r="I45" s="244"/>
       <c r="J45" s="85"/>
       <c r="K45" s="84"/>
       <c r="L45" s="84"/>
       <c r="M45" s="86" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N45" s="83"/>
       <c r="O45" s="80"/>
@@ -5426,20 +5442,20 @@
       <c r="A46" s="80"/>
       <c r="B46" s="114"/>
       <c r="C46" s="87" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" s="88" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="250" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="E46" s="197" t="s">
-        <v>103</v>
-      </c>
-      <c r="F46" s="197"/>
-      <c r="G46" s="197"/>
-      <c r="H46" s="197"/>
-      <c r="I46" s="197"/>
-      <c r="J46" s="197"/>
-      <c r="K46" s="197"/>
+      <c r="F46" s="250"/>
+      <c r="G46" s="250"/>
+      <c r="H46" s="250"/>
+      <c r="I46" s="250"/>
+      <c r="J46" s="250"/>
+      <c r="K46" s="250"/>
       <c r="L46" s="88"/>
       <c r="M46" s="89">
         <v>3</v>
@@ -5451,20 +5467,20 @@
       <c r="A47" s="80"/>
       <c r="B47" s="104"/>
       <c r="C47" s="90" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>104</v>
-      </c>
-      <c r="E47" s="197" t="s">
-        <v>105</v>
-      </c>
-      <c r="F47" s="197"/>
-      <c r="G47" s="197"/>
-      <c r="H47" s="197"/>
-      <c r="I47" s="197"/>
-      <c r="J47" s="197"/>
-      <c r="K47" s="197"/>
+        <v>102</v>
+      </c>
+      <c r="E47" s="250" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="250"/>
+      <c r="G47" s="250"/>
+      <c r="H47" s="250"/>
+      <c r="I47" s="250"/>
+      <c r="J47" s="250"/>
+      <c r="K47" s="250"/>
       <c r="L47" s="88"/>
       <c r="M47" s="91">
         <v>3</v>
@@ -5476,20 +5492,20 @@
       <c r="A48" s="80"/>
       <c r="B48" s="114"/>
       <c r="C48" s="87" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>106</v>
-      </c>
-      <c r="E48" s="197" t="s">
-        <v>107</v>
-      </c>
-      <c r="F48" s="197"/>
-      <c r="G48" s="197"/>
-      <c r="H48" s="197"/>
-      <c r="I48" s="197"/>
-      <c r="J48" s="197"/>
-      <c r="K48" s="197"/>
+        <v>104</v>
+      </c>
+      <c r="E48" s="250" t="s">
+        <v>105</v>
+      </c>
+      <c r="F48" s="250"/>
+      <c r="G48" s="250"/>
+      <c r="H48" s="250"/>
+      <c r="I48" s="250"/>
+      <c r="J48" s="250"/>
+      <c r="K48" s="250"/>
       <c r="L48" s="88"/>
       <c r="M48" s="89">
         <v>3</v>
@@ -5501,20 +5517,20 @@
       <c r="A49" s="80"/>
       <c r="B49" s="104"/>
       <c r="C49" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="93" t="s">
-        <v>109</v>
-      </c>
-      <c r="E49" s="191" t="s">
-        <v>110</v>
-      </c>
-      <c r="F49" s="191"/>
-      <c r="G49" s="191"/>
-      <c r="H49" s="191"/>
-      <c r="I49" s="191"/>
-      <c r="J49" s="191"/>
-      <c r="K49" s="191"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="249"/>
+      <c r="H49" s="249"/>
+      <c r="I49" s="249"/>
+      <c r="J49" s="249"/>
+      <c r="K49" s="249"/>
       <c r="L49" s="93"/>
       <c r="M49" s="94">
         <v>3</v>
@@ -5526,20 +5542,20 @@
       <c r="A50" s="80"/>
       <c r="B50" s="114"/>
       <c r="C50" s="95" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D50" s="96" t="s">
-        <v>111</v>
-      </c>
-      <c r="E50" s="198" t="s">
-        <v>112</v>
-      </c>
-      <c r="F50" s="198"/>
-      <c r="G50" s="198"/>
-      <c r="H50" s="198"/>
-      <c r="I50" s="198"/>
-      <c r="J50" s="198"/>
-      <c r="K50" s="198"/>
+        <v>109</v>
+      </c>
+      <c r="E50" s="248" t="s">
+        <v>110</v>
+      </c>
+      <c r="F50" s="248"/>
+      <c r="G50" s="248"/>
+      <c r="H50" s="248"/>
+      <c r="I50" s="248"/>
+      <c r="J50" s="248"/>
+      <c r="K50" s="248"/>
       <c r="L50" s="96"/>
       <c r="M50" s="97">
         <v>3</v>
@@ -5551,20 +5567,20 @@
       <c r="A51" s="80"/>
       <c r="B51" s="115"/>
       <c r="C51" s="98" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="93" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="191" t="s">
-        <v>115</v>
-      </c>
-      <c r="F51" s="191"/>
-      <c r="G51" s="191"/>
-      <c r="H51" s="191"/>
-      <c r="I51" s="191"/>
-      <c r="J51" s="191"/>
-      <c r="K51" s="191"/>
+      <c r="F51" s="249"/>
+      <c r="G51" s="249"/>
+      <c r="H51" s="249"/>
+      <c r="I51" s="249"/>
+      <c r="J51" s="249"/>
+      <c r="K51" s="249"/>
       <c r="L51" s="93"/>
       <c r="M51" s="99">
         <v>3</v>
@@ -5576,20 +5592,20 @@
       <c r="A52" s="80"/>
       <c r="B52" s="104"/>
       <c r="C52" s="101" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="96" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" s="248" t="s">
         <v>116</v>
       </c>
-      <c r="D52" s="96" t="s">
-        <v>117</v>
-      </c>
-      <c r="E52" s="198" t="s">
-        <v>118</v>
-      </c>
-      <c r="F52" s="198"/>
-      <c r="G52" s="198"/>
-      <c r="H52" s="198"/>
-      <c r="I52" s="198"/>
-      <c r="J52" s="198"/>
-      <c r="K52" s="198"/>
+      <c r="F52" s="248"/>
+      <c r="G52" s="248"/>
+      <c r="H52" s="248"/>
+      <c r="I52" s="248"/>
+      <c r="J52" s="248"/>
+      <c r="K52" s="248"/>
       <c r="L52" s="96"/>
       <c r="M52" s="102">
         <v>3</v>
@@ -5601,20 +5617,20 @@
       <c r="A53" s="80"/>
       <c r="B53" s="104"/>
       <c r="C53" s="92" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D53" s="93" t="s">
-        <v>119</v>
-      </c>
-      <c r="E53" s="191" t="s">
-        <v>120</v>
-      </c>
-      <c r="F53" s="191"/>
-      <c r="G53" s="191"/>
-      <c r="H53" s="191"/>
-      <c r="I53" s="191"/>
-      <c r="J53" s="191"/>
-      <c r="K53" s="191"/>
+        <v>117</v>
+      </c>
+      <c r="E53" s="249" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="249"/>
+      <c r="G53" s="249"/>
+      <c r="H53" s="249"/>
+      <c r="I53" s="249"/>
+      <c r="J53" s="249"/>
+      <c r="K53" s="249"/>
       <c r="L53" s="93"/>
       <c r="M53" s="94">
         <v>3</v>
@@ -5626,20 +5642,20 @@
       <c r="A54" s="80"/>
       <c r="B54" s="104"/>
       <c r="C54" s="95" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="D54" s="96" t="s">
-        <v>121</v>
-      </c>
-      <c r="E54" s="198" t="s">
-        <v>122</v>
-      </c>
-      <c r="F54" s="198"/>
-      <c r="G54" s="198"/>
-      <c r="H54" s="198"/>
-      <c r="I54" s="198"/>
-      <c r="J54" s="198"/>
-      <c r="K54" s="198"/>
+      <c r="E54" s="248" t="s">
+        <v>120</v>
+      </c>
+      <c r="F54" s="248"/>
+      <c r="G54" s="248"/>
+      <c r="H54" s="248"/>
+      <c r="I54" s="248"/>
+      <c r="J54" s="248"/>
+      <c r="K54" s="248"/>
       <c r="L54" s="96"/>
       <c r="M54" s="97">
         <v>3</v>
@@ -5651,20 +5667,20 @@
       <c r="A55" s="80"/>
       <c r="B55" s="116"/>
       <c r="C55" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D55" s="93" t="s">
+        <v>122</v>
+      </c>
+      <c r="E55" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="D55" s="93" t="s">
-        <v>124</v>
-      </c>
-      <c r="E55" s="191" t="s">
-        <v>125</v>
-      </c>
-      <c r="F55" s="191"/>
-      <c r="G55" s="191"/>
-      <c r="H55" s="191"/>
-      <c r="I55" s="191"/>
-      <c r="J55" s="191"/>
-      <c r="K55" s="191"/>
+      <c r="F55" s="249"/>
+      <c r="G55" s="249"/>
+      <c r="H55" s="249"/>
+      <c r="I55" s="249"/>
+      <c r="J55" s="249"/>
+      <c r="K55" s="249"/>
       <c r="L55" s="93"/>
       <c r="M55" s="99">
         <v>3</v>
@@ -5676,20 +5692,20 @@
       <c r="A56" s="80"/>
       <c r="B56" s="114"/>
       <c r="C56" s="101" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D56" s="96" t="s">
-        <v>126</v>
-      </c>
-      <c r="E56" s="198" t="s">
-        <v>127</v>
-      </c>
-      <c r="F56" s="198"/>
-      <c r="G56" s="198"/>
-      <c r="H56" s="198"/>
-      <c r="I56" s="198"/>
-      <c r="J56" s="198"/>
-      <c r="K56" s="198"/>
+        <v>124</v>
+      </c>
+      <c r="E56" s="248" t="s">
+        <v>125</v>
+      </c>
+      <c r="F56" s="248"/>
+      <c r="G56" s="248"/>
+      <c r="H56" s="248"/>
+      <c r="I56" s="248"/>
+      <c r="J56" s="248"/>
+      <c r="K56" s="248"/>
       <c r="L56" s="96"/>
       <c r="M56" s="102">
         <v>3</v>
@@ -5734,252 +5750,250 @@
     <row r="59" spans="1:15" ht="24" customHeight="1">
       <c r="A59" s="80"/>
       <c r="B59" s="117" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="272" t="s">
-        <v>129</v>
-      </c>
-      <c r="D59" s="272"/>
-      <c r="E59" s="272"/>
+        <v>126</v>
+      </c>
+      <c r="C59" s="243" t="s">
+        <v>127</v>
+      </c>
+      <c r="D59" s="243"/>
+      <c r="E59" s="243"/>
       <c r="F59" s="105" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L59" s="104"/>
       <c r="M59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O59" s="80"/>
     </row>
     <row r="60" spans="1:15" ht="15.75" customHeight="1">
       <c r="A60" s="80"/>
       <c r="B60" s="117" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60" s="106" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="D60" s="106" t="s">
+        <v>129</v>
+      </c>
+      <c r="E60" s="247" t="s">
         <v>130</v>
       </c>
-      <c r="D60" s="106" t="s">
+      <c r="F60" s="247"/>
+      <c r="G60" s="247"/>
+      <c r="H60" s="247"/>
+      <c r="I60" s="107" t="s">
         <v>131</v>
-      </c>
-      <c r="E60" s="199" t="s">
-        <v>132</v>
-      </c>
-      <c r="F60" s="199"/>
-      <c r="G60" s="199"/>
-      <c r="H60" s="199"/>
-      <c r="I60" s="107" t="s">
-        <v>133</v>
       </c>
       <c r="J60" s="106"/>
       <c r="K60" s="106"/>
       <c r="L60" s="106"/>
       <c r="M60" s="106"/>
       <c r="N60" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O60" s="80"/>
     </row>
     <row r="61" spans="1:15" ht="48.75" customHeight="1">
       <c r="A61" s="80"/>
       <c r="B61" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C61" s="108">
         <v>1</v>
       </c>
       <c r="D61" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="E61" s="253" t="s">
+        <v>133</v>
+      </c>
+      <c r="F61" s="253"/>
+      <c r="G61" s="253"/>
+      <c r="H61" s="253"/>
+      <c r="I61" s="254" t="s">
         <v>134</v>
       </c>
-      <c r="E61" s="186" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61" s="186"/>
-      <c r="G61" s="186"/>
-      <c r="H61" s="186"/>
-      <c r="I61" s="187" t="s">
-        <v>136</v>
-      </c>
-      <c r="J61" s="187"/>
-      <c r="K61" s="187"/>
-      <c r="L61" s="187"/>
-      <c r="M61" s="187"/>
+      <c r="J61" s="254"/>
+      <c r="K61" s="254"/>
+      <c r="L61" s="254"/>
+      <c r="M61" s="254"/>
       <c r="N61" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O61" s="80"/>
     </row>
     <row r="62" spans="1:15" ht="47.25" customHeight="1">
       <c r="A62" s="80"/>
       <c r="B62" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C62" s="110">
         <v>2</v>
       </c>
       <c r="D62" s="111" t="s">
+        <v>135</v>
+      </c>
+      <c r="E62" s="251" t="s">
+        <v>136</v>
+      </c>
+      <c r="F62" s="251"/>
+      <c r="G62" s="251"/>
+      <c r="H62" s="251"/>
+      <c r="I62" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="184" t="s">
-        <v>138</v>
-      </c>
-      <c r="F62" s="184"/>
-      <c r="G62" s="184"/>
-      <c r="H62" s="184"/>
-      <c r="I62" s="185" t="s">
-        <v>139</v>
-      </c>
-      <c r="J62" s="185"/>
-      <c r="K62" s="185"/>
-      <c r="L62" s="185"/>
-      <c r="M62" s="185"/>
+      <c r="J62" s="252"/>
+      <c r="K62" s="252"/>
+      <c r="L62" s="252"/>
+      <c r="M62" s="252"/>
       <c r="N62" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O62" s="80"/>
     </row>
     <row r="63" spans="1:15" ht="42" customHeight="1">
       <c r="A63" s="80"/>
       <c r="B63" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C63" s="108">
         <v>3</v>
       </c>
       <c r="D63" s="109" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" s="253" t="s">
+        <v>139</v>
+      </c>
+      <c r="F63" s="253"/>
+      <c r="G63" s="253"/>
+      <c r="H63" s="253"/>
+      <c r="I63" s="254" t="s">
         <v>140</v>
       </c>
-      <c r="E63" s="186" t="s">
-        <v>141</v>
-      </c>
-      <c r="F63" s="186"/>
-      <c r="G63" s="186"/>
-      <c r="H63" s="186"/>
-      <c r="I63" s="187" t="s">
-        <v>142</v>
-      </c>
-      <c r="J63" s="187"/>
-      <c r="K63" s="187"/>
-      <c r="L63" s="187"/>
-      <c r="M63" s="187"/>
+      <c r="J63" s="254"/>
+      <c r="K63" s="254"/>
+      <c r="L63" s="254"/>
+      <c r="M63" s="254"/>
       <c r="N63" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O63" s="80"/>
     </row>
     <row r="64" spans="1:15" ht="42" customHeight="1">
       <c r="A64" s="80"/>
       <c r="B64" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C64" s="110">
         <v>4</v>
       </c>
       <c r="D64" s="111" t="s">
+        <v>141</v>
+      </c>
+      <c r="E64" s="251" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="251"/>
+      <c r="G64" s="251"/>
+      <c r="H64" s="251"/>
+      <c r="I64" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="E64" s="184" t="s">
-        <v>144</v>
-      </c>
-      <c r="F64" s="184"/>
-      <c r="G64" s="184"/>
-      <c r="H64" s="184"/>
-      <c r="I64" s="185" t="s">
-        <v>145</v>
-      </c>
-      <c r="J64" s="185"/>
-      <c r="K64" s="185"/>
-      <c r="L64" s="185"/>
-      <c r="M64" s="185"/>
+      <c r="J64" s="252"/>
+      <c r="K64" s="252"/>
+      <c r="L64" s="252"/>
+      <c r="M64" s="252"/>
       <c r="N64" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O64" s="80"/>
     </row>
     <row r="65" spans="1:15" ht="36" customHeight="1">
       <c r="A65" s="80"/>
       <c r="B65" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C65" s="108">
         <v>5</v>
       </c>
       <c r="D65" s="109" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" s="253" t="s">
+        <v>145</v>
+      </c>
+      <c r="F65" s="253"/>
+      <c r="G65" s="253"/>
+      <c r="H65" s="253"/>
+      <c r="I65" s="254" t="s">
         <v>146</v>
       </c>
-      <c r="E65" s="186" t="s">
-        <v>147</v>
-      </c>
-      <c r="F65" s="186"/>
-      <c r="G65" s="186"/>
-      <c r="H65" s="186"/>
-      <c r="I65" s="187" t="s">
-        <v>148</v>
-      </c>
-      <c r="J65" s="187"/>
-      <c r="K65" s="187"/>
-      <c r="L65" s="187"/>
-      <c r="M65" s="187"/>
-      <c r="N65" s="104" t="s">
-        <v>128</v>
-      </c>
+      <c r="J65" s="254"/>
+      <c r="K65" s="254"/>
+      <c r="L65" s="254"/>
+      <c r="M65" s="254"/>
+      <c r="N65" s="104"/>
       <c r="O65" s="80"/>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1">
       <c r="A66" s="80"/>
       <c r="B66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L66" s="104"/>
       <c r="M66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O66" s="80"/>
     </row>
@@ -6957,73 +6971,6 @@
     <protectedRange algorithmName="SHA-512" hashValue="NcQe0VjxFnxU9SziGkmWOoYUYoQ0T62vv+WqFE1sowJD2+jDiq1RKEMS6wObDPCk433k/JG1CTU3j62rwNOzdg==" saltValue="OlYFZTFPx5QDCqKlqXj8fw==" spinCount="100000" sqref="U39 H39" name="Range1_2_1_7"/>
   </protectedRanges>
   <mergeCells count="83">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:K7"/>
-    <mergeCell ref="L3:L7"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="N3:N7"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:M10"/>
-    <mergeCell ref="M3:M7"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D25:M25"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:K37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E52:K52"/>
-    <mergeCell ref="E53:K53"/>
-    <mergeCell ref="E54:K54"/>
-    <mergeCell ref="E55:K55"/>
-    <mergeCell ref="E56:K56"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="E46:K46"/>
-    <mergeCell ref="E47:K47"/>
-    <mergeCell ref="E48:K48"/>
-    <mergeCell ref="E49:K49"/>
-    <mergeCell ref="E50:K50"/>
     <mergeCell ref="E64:H64"/>
     <mergeCell ref="I64:M64"/>
     <mergeCell ref="E65:H65"/>
@@ -7040,125 +6987,192 @@
     <mergeCell ref="L41:L42"/>
     <mergeCell ref="M41:M42"/>
     <mergeCell ref="D29:K29"/>
+    <mergeCell ref="E46:K46"/>
+    <mergeCell ref="E47:K47"/>
+    <mergeCell ref="E48:K48"/>
+    <mergeCell ref="E49:K49"/>
+    <mergeCell ref="E50:K50"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E52:K52"/>
+    <mergeCell ref="E53:K53"/>
+    <mergeCell ref="E54:K54"/>
+    <mergeCell ref="E55:K55"/>
+    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:K37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:K33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D25:M25"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D17:K17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="N3:N7"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:M10"/>
+    <mergeCell ref="M3:M7"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:K7"/>
+    <mergeCell ref="L3:L7"/>
   </mergeCells>
   <conditionalFormatting sqref="L15 L27">
-    <cfRule type="cellIs" dxfId="83" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="40" operator="equal">
+      <formula>"INSUFFICIENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="39" operator="equal">
+      <formula>"SUFFICIENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="38" operator="equal">
+      <formula>"GOOD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="37" operator="equal">
+      <formula>"EXCELLENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="42" operator="equal">
       <formula>"POOR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="41" operator="equal">
       <formula>"MISSING"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="40" operator="equal">
-      <formula>"INSUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="39" operator="equal">
-      <formula>"SUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="38" operator="equal">
-      <formula>"GOOD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="37" operator="equal">
-      <formula>"EXCELLENT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="77" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="11" operator="equal">
+      <formula>"MISSING"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="7" operator="equal">
       <formula>"EXCELLENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="8" operator="equal">
       <formula>"GOOD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="9" operator="equal">
       <formula>"SUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="10" operator="equal">
       <formula>"INSUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="11" operator="equal">
-      <formula>"MISSING"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="72" priority="12" operator="equal">
       <formula>"POOR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
-      <formula>"EXCELLENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="equal">
       <formula>"GOOD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="3" operator="equal">
       <formula>"SUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="4" operator="equal">
       <formula>"INSUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="5" operator="equal">
       <formula>"MISSING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="6" operator="equal">
       <formula>"POOR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="1" operator="equal">
+      <formula>"EXCELLENT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L31">
     <cfRule type="cellIs" dxfId="65" priority="28" operator="equal">
       <formula>"EXCELLENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="33" operator="equal">
-      <formula>"POOR"</formula>
+    <cfRule type="cellIs" dxfId="64" priority="29" operator="equal">
+      <formula>"GOOD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="32" operator="equal">
-      <formula>"MISSING"</formula>
+    <cfRule type="cellIs" dxfId="63" priority="30" operator="equal">
+      <formula>"SUFFICIENT"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="62" priority="31" operator="equal">
       <formula>"INSUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="30" operator="equal">
-      <formula>"SUFFICIENT"</formula>
+    <cfRule type="cellIs" dxfId="61" priority="33" operator="equal">
+      <formula>"POOR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="29" operator="equal">
-      <formula>"GOOD"</formula>
+    <cfRule type="cellIs" dxfId="60" priority="32" operator="equal">
+      <formula>"MISSING"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35">
-    <cfRule type="cellIs" dxfId="59" priority="22" operator="equal">
-      <formula>"EXCELLENT"</formula>
+    <cfRule type="cellIs" dxfId="59" priority="23" operator="equal">
+      <formula>"GOOD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="24" operator="equal">
+      <formula>"SUFFICIENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="25" operator="equal">
+      <formula>"INSUFFICIENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="26" operator="equal">
       <formula>"MISSING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="27" operator="equal">
       <formula>"POOR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="25" operator="equal">
-      <formula>"INSUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="24" operator="equal">
-      <formula>"SUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="23" operator="equal">
-      <formula>"GOOD"</formula>
+    <cfRule type="cellIs" dxfId="54" priority="22" operator="equal">
+      <formula>"EXCELLENT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L39">
-    <cfRule type="cellIs" dxfId="53" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
+      <formula>"EXCELLENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="17" operator="equal">
+      <formula>"GOOD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="21" operator="equal">
       <formula>"POOR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="20" operator="equal">
       <formula>"MISSING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="19" operator="equal">
       <formula>"INSUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="18" operator="equal">
       <formula>"SUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="17" operator="equal">
-      <formula>"GOOD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="16" operator="equal">
-      <formula>"EXCELLENT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3">
@@ -7176,11 +7190,11 @@
     <cfRule type="expression" dxfId="44" priority="13" stopIfTrue="1">
       <formula>$L$3&gt;5.5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="14" stopIfTrue="1">
+      <formula>($L$3&lt;5.5) &amp; ($L$3&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="15" stopIfTrue="1">
       <formula>$L$3=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="14" stopIfTrue="1">
-      <formula>($L$3&lt;5.5) &amp; ($L$3&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -7216,26 +7230,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y1019"/>
-  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="45" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" style="45" customWidth="1"/>
+    <col min="1" max="2" width="9.1796875" style="45" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" style="45" customWidth="1"/>
     <col min="4" max="4" width="27" style="45" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="45" customWidth="1"/>
-    <col min="6" max="6" width="37.85546875" style="45" customWidth="1"/>
-    <col min="7" max="7" width="29.28515625" style="45" customWidth="1"/>
-    <col min="8" max="8" width="29.7109375" style="45" customWidth="1"/>
-    <col min="9" max="9" width="33.140625" style="45" customWidth="1"/>
-    <col min="10" max="11" width="36.7109375" style="45" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" style="45" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" style="45" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" style="45" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" style="45" customWidth="1"/>
-    <col min="16" max="25" width="14.42578125" style="45" customWidth="1"/>
-    <col min="26" max="16384" width="12.42578125" style="45"/>
+    <col min="5" max="5" width="22.7265625" style="45" customWidth="1"/>
+    <col min="6" max="6" width="37.81640625" style="45" customWidth="1"/>
+    <col min="7" max="7" width="29.26953125" style="45" customWidth="1"/>
+    <col min="8" max="8" width="29.7265625" style="45" customWidth="1"/>
+    <col min="9" max="9" width="33.1796875" style="45" customWidth="1"/>
+    <col min="10" max="11" width="36.7265625" style="45" customWidth="1"/>
+    <col min="12" max="12" width="17.1796875" style="45" customWidth="1"/>
+    <col min="13" max="13" width="6.7265625" style="45" customWidth="1"/>
+    <col min="14" max="14" width="17.1796875" style="45" customWidth="1"/>
+    <col min="15" max="15" width="6.7265625" style="45" customWidth="1"/>
+    <col min="16" max="25" width="14.453125" style="45" customWidth="1"/>
+    <col min="26" max="16384" width="12.453125" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A1" s="80"/>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -7252,22 +7266,22 @@
       <c r="N1" s="80"/>
       <c r="O1" s="80"/>
     </row>
-    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A2" s="80"/>
       <c r="B2" s="47"/>
-      <c r="C2" s="249"/>
-      <c r="D2" s="268"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="185"/>
       <c r="E2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="250" t="s">
+      <c r="F2" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="250"/>
-      <c r="J2" s="250"/>
-      <c r="K2" s="250"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="186"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="186"/>
       <c r="L2" s="66" t="s">
         <v>2</v>
       </c>
@@ -7287,117 +7301,117 @@
       <c r="X2" s="48"/>
       <c r="Y2" s="48"/>
     </row>
-    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="3" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A3" s="80"/>
       <c r="B3" s="49"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="246"/>
+      <c r="D3" s="188"/>
       <c r="E3" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="189" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="251" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="252"/>
-      <c r="H3" s="252"/>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="254">
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="190"/>
+      <c r="J3" s="190"/>
+      <c r="K3" s="191"/>
+      <c r="L3" s="192">
         <v>0</v>
       </c>
-      <c r="M3" s="248"/>
-      <c r="N3" s="242" t="str">
+      <c r="M3" s="202"/>
+      <c r="N3" s="198" t="str">
         <f>IF(L3&gt;=5.5,"PASS",IF(L3&gt;0,"FAIL","M/O"))</f>
         <v>M/O</v>
       </c>
       <c r="O3" s="80"/>
     </row>
-    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A4" s="80"/>
       <c r="B4" s="49"/>
-      <c r="C4" s="245" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="246"/>
+      <c r="C4" s="187" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="188"/>
       <c r="E4" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="251"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="253"/>
-      <c r="L4" s="269"/>
-      <c r="M4" s="270"/>
-      <c r="N4" s="243"/>
+        <v>148</v>
+      </c>
+      <c r="F4" s="189"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="190"/>
+      <c r="K4" s="191"/>
+      <c r="L4" s="193"/>
+      <c r="M4" s="203"/>
+      <c r="N4" s="199"/>
       <c r="O4" s="80"/>
     </row>
-    <row r="5" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A5" s="80"/>
       <c r="B5" s="49"/>
-      <c r="C5" s="245" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="246"/>
+      <c r="C5" s="187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="188"/>
       <c r="E5" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="251"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="253"/>
-      <c r="L5" s="269"/>
-      <c r="M5" s="270"/>
-      <c r="N5" s="243"/>
+        <v>8</v>
+      </c>
+      <c r="F5" s="189"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="190"/>
+      <c r="J5" s="190"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="193"/>
+      <c r="M5" s="203"/>
+      <c r="N5" s="199"/>
       <c r="O5" s="80"/>
     </row>
-    <row r="6" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A6" s="80"/>
       <c r="B6" s="49"/>
-      <c r="C6" s="245" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="246"/>
+      <c r="C6" s="187" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="188"/>
       <c r="E6" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="251"/>
-      <c r="G6" s="252"/>
-      <c r="H6" s="252"/>
-      <c r="I6" s="252"/>
-      <c r="J6" s="252"/>
-      <c r="K6" s="253"/>
-      <c r="L6" s="269"/>
-      <c r="M6" s="270"/>
-      <c r="N6" s="243"/>
+        <v>10</v>
+      </c>
+      <c r="F6" s="189"/>
+      <c r="G6" s="190"/>
+      <c r="H6" s="190"/>
+      <c r="I6" s="190"/>
+      <c r="J6" s="190"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="193"/>
+      <c r="M6" s="203"/>
+      <c r="N6" s="199"/>
       <c r="O6" s="80"/>
     </row>
-    <row r="7" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A7" s="80"/>
       <c r="B7" s="49"/>
-      <c r="C7" s="245" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="246"/>
+      <c r="C7" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="188"/>
       <c r="E7" s="60"/>
-      <c r="F7" s="251"/>
-      <c r="G7" s="252"/>
-      <c r="H7" s="252"/>
-      <c r="I7" s="252"/>
-      <c r="J7" s="252"/>
-      <c r="K7" s="253"/>
-      <c r="L7" s="269"/>
-      <c r="M7" s="270"/>
-      <c r="N7" s="244"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="191"/>
+      <c r="L7" s="193"/>
+      <c r="M7" s="203"/>
+      <c r="N7" s="200"/>
       <c r="O7" s="80"/>
     </row>
-    <row r="8" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A8" s="80"/>
       <c r="B8" s="46"/>
       <c r="C8" s="46"/>
@@ -7431,22 +7445,22 @@
       <c r="N9" s="80"/>
       <c r="O9" s="80"/>
     </row>
-    <row r="10" spans="1:25" ht="24.95" customHeight="1">
+    <row r="10" spans="1:25" ht="25" customHeight="1">
       <c r="A10" s="80"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="247" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="247"/>
-      <c r="E10" s="247"/>
-      <c r="F10" s="247"/>
-      <c r="G10" s="247"/>
-      <c r="H10" s="247"/>
-      <c r="I10" s="247"/>
-      <c r="J10" s="247"/>
-      <c r="K10" s="247"/>
-      <c r="L10" s="247"/>
-      <c r="M10" s="247"/>
+      <c r="C10" s="201" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="201"/>
+      <c r="E10" s="201"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="201"/>
+      <c r="H10" s="201"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="201"/>
+      <c r="K10" s="201"/>
+      <c r="L10" s="201"/>
+      <c r="M10" s="201"/>
       <c r="N10" s="46"/>
       <c r="O10" s="80"/>
     </row>
@@ -7455,27 +7469,27 @@
       <c r="B11" s="46"/>
       <c r="C11" s="50"/>
       <c r="D11" s="51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E11" s="52"/>
       <c r="F11" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="205" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="205"/>
+      <c r="I11" s="205"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="205"/>
+      <c r="L11" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="228" t="s">
+      <c r="M11" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="228"/>
-      <c r="I11" s="228"/>
-      <c r="J11" s="228"/>
-      <c r="K11" s="228"/>
-      <c r="L11" s="50" t="s">
+      <c r="N11" s="50" t="s">
         <v>18</v>
-      </c>
-      <c r="M11" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" s="50" t="s">
-        <v>20</v>
       </c>
       <c r="O11" s="80"/>
     </row>
@@ -7500,48 +7514,48 @@
       <c r="A13" s="80"/>
       <c r="B13" s="46"/>
       <c r="C13" s="118" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="229" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="230"/>
-      <c r="F13" s="230"/>
-      <c r="G13" s="230"/>
-      <c r="H13" s="230"/>
-      <c r="I13" s="230"/>
-      <c r="J13" s="230"/>
-      <c r="K13" s="230"/>
+        <v>19</v>
+      </c>
+      <c r="D13" s="206" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="207"/>
+      <c r="F13" s="207"/>
+      <c r="G13" s="207"/>
+      <c r="H13" s="207"/>
+      <c r="I13" s="207"/>
+      <c r="J13" s="207"/>
+      <c r="K13" s="207"/>
       <c r="L13" s="53"/>
       <c r="M13" s="53"/>
       <c r="N13" s="54"/>
       <c r="O13" s="80"/>
     </row>
-    <row r="14" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A14" s="80"/>
       <c r="B14" s="46"/>
       <c r="C14" s="118"/>
-      <c r="D14" s="231"/>
-      <c r="E14" s="232"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="209"/>
       <c r="F14" s="139" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="143" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="143" t="s">
+      <c r="I14" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="143" t="s">
+      <c r="J14" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="143" t="s">
+      <c r="K14" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="143" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" s="167"/>
+      <c r="L14" s="159"/>
       <c r="M14" s="121"/>
       <c r="N14" s="122"/>
       <c r="O14" s="80"/>
@@ -7553,46 +7567,46 @@
       <c r="D15" s="210" t="s">
         <v>149</v>
       </c>
-      <c r="E15" s="203"/>
-      <c r="F15" s="160" t="s">
+      <c r="E15" s="211"/>
+      <c r="F15" s="152" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="166" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="166" t="s">
+      <c r="G15" s="158" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="158" t="s">
         <v>151</v>
       </c>
-      <c r="I15" s="166" t="s">
+      <c r="I15" s="158" t="s">
         <v>152</v>
       </c>
-      <c r="J15" s="166" t="s">
+      <c r="J15" s="158" t="s">
         <v>153</v>
       </c>
-      <c r="K15" s="166" t="s">
+      <c r="K15" s="158" t="s">
         <v>154</v>
       </c>
-      <c r="L15" s="162">
+      <c r="L15" s="154">
         <v>0</v>
       </c>
-      <c r="M15" s="239" t="s">
-        <v>36</v>
+      <c r="M15" s="194" t="s">
+        <v>34</v>
       </c>
       <c r="N15" s="126">
         <v>15</v>
       </c>
       <c r="O15" s="80"/>
     </row>
-    <row r="16" spans="1:25" ht="24.95" customHeight="1">
+    <row r="16" spans="1:25" ht="25" customHeight="1">
       <c r="A16" s="80"/>
       <c r="B16" s="46"/>
       <c r="C16" s="112"/>
-      <c r="D16" s="241" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="204"/>
+      <c r="D16" s="196" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="197"/>
       <c r="F16" s="140" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G16" s="144">
         <v>0</v>
@@ -7609,8 +7623,8 @@
       <c r="K16" s="144">
         <v>0</v>
       </c>
-      <c r="L16" s="168"/>
-      <c r="M16" s="240"/>
+      <c r="L16" s="160"/>
+      <c r="M16" s="195"/>
       <c r="N16" s="127"/>
       <c r="O16" s="80"/>
       <c r="P16" s="45">
@@ -7622,48 +7636,48 @@
       <c r="A17" s="80"/>
       <c r="B17" s="46"/>
       <c r="C17" s="118" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="229" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="230"/>
-      <c r="F17" s="230"/>
-      <c r="G17" s="230"/>
-      <c r="H17" s="230"/>
-      <c r="I17" s="230"/>
-      <c r="J17" s="230"/>
-      <c r="K17" s="230"/>
+        <v>19</v>
+      </c>
+      <c r="D17" s="206" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="207"/>
+      <c r="F17" s="207"/>
+      <c r="G17" s="207"/>
+      <c r="H17" s="207"/>
+      <c r="I17" s="207"/>
+      <c r="J17" s="207"/>
+      <c r="K17" s="207"/>
       <c r="L17" s="77"/>
       <c r="M17" s="78"/>
       <c r="N17" s="79"/>
       <c r="O17" s="80"/>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A18" s="80"/>
       <c r="B18" s="46"/>
       <c r="C18" s="118"/>
-      <c r="D18" s="231"/>
-      <c r="E18" s="232"/>
+      <c r="D18" s="208"/>
+      <c r="E18" s="209"/>
       <c r="F18" s="139" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G18" s="143" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="143" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="H18" s="143" t="s">
+      <c r="J18" s="143" t="s">
         <v>68</v>
       </c>
-      <c r="I18" s="143" t="s">
+      <c r="K18" s="143" t="s">
         <v>69</v>
       </c>
-      <c r="J18" s="143" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="143" t="s">
-        <v>71</v>
-      </c>
-      <c r="L18" s="161"/>
+      <c r="L18" s="153"/>
       <c r="M18" s="124"/>
       <c r="N18" s="125"/>
       <c r="O18" s="80"/>
@@ -7673,35 +7687,35 @@
       <c r="B19" s="46"/>
       <c r="C19" s="113"/>
       <c r="D19" s="210"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="160"/>
-      <c r="G19" s="164"/>
-      <c r="H19" s="164"/>
-      <c r="I19" s="164"/>
-      <c r="J19" s="164"/>
-      <c r="K19" s="164"/>
-      <c r="L19" s="162">
+      <c r="E19" s="211"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="156"/>
+      <c r="H19" s="156"/>
+      <c r="I19" s="156"/>
+      <c r="J19" s="156"/>
+      <c r="K19" s="156"/>
+      <c r="L19" s="154">
         <f>IF(F20="Yes",SUM(G20:K20)*2,0)</f>
         <v>0</v>
       </c>
       <c r="M19" s="124" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N19" s="125">
         <v>0</v>
       </c>
       <c r="O19" s="80"/>
     </row>
-    <row r="20" spans="1:25" ht="24.95" customHeight="1">
+    <row r="20" spans="1:25" ht="25" customHeight="1">
       <c r="A20" s="80"/>
       <c r="B20" s="46"/>
       <c r="C20" s="112"/>
-      <c r="D20" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="205"/>
+      <c r="D20" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="213"/>
       <c r="F20" s="140" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G20" s="144">
         <v>0</v>
@@ -7709,7 +7723,7 @@
       <c r="H20" s="144">
         <v>0</v>
       </c>
-      <c r="I20" s="163">
+      <c r="I20" s="155">
         <v>0</v>
       </c>
       <c r="J20" s="144">
@@ -7736,18 +7750,18 @@
       <c r="A21" s="80"/>
       <c r="B21" s="46"/>
       <c r="C21" s="118" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="258" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="261" t="s">
         <v>155</v>
       </c>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
+      <c r="E21" s="261"/>
+      <c r="F21" s="261"/>
+      <c r="G21" s="261"/>
+      <c r="H21" s="261"/>
+      <c r="I21" s="261"/>
+      <c r="J21" s="261"/>
+      <c r="K21" s="261"/>
       <c r="L21" s="123"/>
       <c r="M21" s="124"/>
       <c r="N21" s="125"/>
@@ -7762,27 +7776,27 @@
       <c r="X21"/>
       <c r="Y21"/>
     </row>
-    <row r="22" spans="1:25" ht="24.95" customHeight="1">
+    <row r="22" spans="1:25" ht="25" customHeight="1">
       <c r="A22" s="80"/>
       <c r="B22" s="46"/>
       <c r="C22" s="118"/>
-      <c r="D22" s="207"/>
-      <c r="E22" s="207"/>
+      <c r="D22" s="204"/>
+      <c r="E22" s="204"/>
       <c r="F22" s="139" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="255" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" s="255"/>
+        <v>21</v>
+      </c>
+      <c r="G22" s="263" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="263"/>
       <c r="I22" s="142" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="120" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="119" t="s">
         <v>42</v>
-      </c>
-      <c r="J22" s="120" t="s">
-        <v>43</v>
-      </c>
-      <c r="K22" s="119" t="s">
-        <v>44</v>
       </c>
       <c r="L22" s="123"/>
       <c r="M22" s="124"/>
@@ -7803,31 +7817,31 @@
       <c r="B23" s="46"/>
       <c r="C23" s="112"/>
       <c r="D23" s="210" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="203"/>
+        <v>44</v>
+      </c>
+      <c r="E23" s="211"/>
       <c r="F23" s="135" t="s">
         <v>156</v>
       </c>
-      <c r="G23" s="256" t="s">
+      <c r="G23" s="264" t="s">
         <v>157</v>
       </c>
-      <c r="H23" s="257"/>
+      <c r="H23" s="265"/>
       <c r="I23" s="141" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J23" s="141" t="s">
         <v>158</v>
       </c>
       <c r="K23" s="138" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L23" s="123">
         <f>IF(F24="Yes",SUM(G24:K24),0)</f>
         <v>0</v>
       </c>
       <c r="M23" s="124" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N23" s="125">
         <v>10</v>
@@ -7843,21 +7857,21 @@
       <c r="X23"/>
       <c r="Y23"/>
     </row>
-    <row r="24" spans="1:25" ht="24.95" customHeight="1">
+    <row r="24" spans="1:25" ht="25" customHeight="1">
       <c r="A24" s="80"/>
       <c r="B24" s="46"/>
       <c r="C24" s="112"/>
-      <c r="D24" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="205"/>
+      <c r="D24" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="213"/>
       <c r="F24" s="140" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="259">
+        <v>36</v>
+      </c>
+      <c r="G24" s="262">
         <v>0</v>
       </c>
-      <c r="H24" s="259"/>
+      <c r="H24" s="262"/>
       <c r="I24" s="134">
         <v>0</v>
       </c>
@@ -7885,18 +7899,18 @@
       <c r="A25" s="80"/>
       <c r="B25" s="46"/>
       <c r="C25" s="118" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="233" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="214" t="s">
         <v>159</v>
       </c>
-      <c r="E25" s="271"/>
-      <c r="F25" s="271"/>
-      <c r="G25" s="271"/>
-      <c r="H25" s="271"/>
-      <c r="I25" s="271"/>
-      <c r="J25" s="271"/>
-      <c r="K25" s="271"/>
+      <c r="E25" s="215"/>
+      <c r="F25" s="215"/>
+      <c r="G25" s="215"/>
+      <c r="H25" s="215"/>
+      <c r="I25" s="215"/>
+      <c r="J25" s="215"/>
+      <c r="K25" s="215"/>
       <c r="L25" s="67"/>
       <c r="M25" s="69"/>
       <c r="N25" s="68"/>
@@ -7911,24 +7925,24 @@
       <c r="X25"/>
       <c r="Y25"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A26" s="80"/>
       <c r="B26" s="46"/>
       <c r="C26" s="118"/>
-      <c r="D26" s="207"/>
-      <c r="E26" s="207"/>
+      <c r="D26" s="204"/>
+      <c r="E26" s="204"/>
       <c r="F26" s="120" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="218" t="s">
-        <v>55</v>
-      </c>
-      <c r="H26" s="219"/>
-      <c r="I26" s="220"/>
-      <c r="J26" s="218" t="s">
-        <v>56</v>
-      </c>
-      <c r="K26" s="220"/>
+        <v>21</v>
+      </c>
+      <c r="G26" s="221" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="222"/>
+      <c r="I26" s="223"/>
+      <c r="J26" s="221" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" s="223"/>
       <c r="L26" s="73"/>
       <c r="M26" s="76"/>
       <c r="N26" s="71"/>
@@ -7948,27 +7962,27 @@
       <c r="B27" s="46"/>
       <c r="C27" s="112"/>
       <c r="D27" s="210" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="203"/>
+        <v>55</v>
+      </c>
+      <c r="E27" s="211"/>
       <c r="F27" s="135" t="s">
         <v>160</v>
       </c>
-      <c r="G27" s="211" t="s">
+      <c r="G27" s="233" t="s">
         <v>161</v>
       </c>
-      <c r="H27" s="212"/>
-      <c r="I27" s="213"/>
-      <c r="J27" s="211" t="s">
-        <v>59</v>
-      </c>
-      <c r="K27" s="212"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="235"/>
+      <c r="J27" s="233" t="s">
+        <v>57</v>
+      </c>
+      <c r="K27" s="234"/>
       <c r="L27" s="123">
         <f>IF(F28="Yes",SUM(G28:K28),0)</f>
         <v>0</v>
       </c>
       <c r="M27" s="128" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N27" s="122">
         <v>10</v>
@@ -7984,26 +7998,26 @@
       <c r="X27"/>
       <c r="Y27"/>
     </row>
-    <row r="28" spans="1:25" ht="24.95" customHeight="1">
+    <row r="28" spans="1:25" ht="25" customHeight="1">
       <c r="A28" s="80"/>
       <c r="B28" s="46"/>
       <c r="C28" s="112"/>
-      <c r="D28" s="214" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="204"/>
+      <c r="D28" s="236" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="197"/>
       <c r="F28" s="132" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="215">
+        <v>36</v>
+      </c>
+      <c r="G28" s="237">
         <v>0</v>
       </c>
-      <c r="H28" s="216"/>
-      <c r="I28" s="217"/>
-      <c r="J28" s="215">
+      <c r="H28" s="238"/>
+      <c r="I28" s="239"/>
+      <c r="J28" s="237">
         <v>0</v>
       </c>
-      <c r="K28" s="217"/>
+      <c r="K28" s="239"/>
       <c r="L28" s="129"/>
       <c r="M28" s="130"/>
       <c r="N28" s="131"/>
@@ -8022,18 +8036,18 @@
       <c r="A29" s="80"/>
       <c r="B29" s="46"/>
       <c r="C29" s="118" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="196" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="271"/>
-      <c r="F29" s="271"/>
-      <c r="G29" s="271"/>
-      <c r="H29" s="271"/>
-      <c r="I29" s="271"/>
-      <c r="J29" s="271"/>
-      <c r="K29" s="271"/>
+        <v>63</v>
+      </c>
+      <c r="D29" s="212" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="215"/>
+      <c r="F29" s="215"/>
+      <c r="G29" s="215"/>
+      <c r="H29" s="215"/>
+      <c r="I29" s="215"/>
+      <c r="J29" s="215"/>
+      <c r="K29" s="215"/>
       <c r="L29" s="74"/>
       <c r="M29" s="69"/>
       <c r="N29" s="72"/>
@@ -8048,29 +8062,29 @@
       <c r="X29"/>
       <c r="Y29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A30" s="80"/>
       <c r="B30" s="46"/>
       <c r="C30" s="118"/>
-      <c r="D30" s="207"/>
-      <c r="E30" s="207"/>
+      <c r="D30" s="204"/>
+      <c r="E30" s="204"/>
       <c r="F30" s="120" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="H30" s="120" t="s">
+        <v>66</v>
+      </c>
+      <c r="I30" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="H30" s="120" t="s">
+      <c r="J30" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="I30" s="120" t="s">
+      <c r="K30" s="120" t="s">
         <v>69</v>
-      </c>
-      <c r="J30" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="K30" s="120" t="s">
-        <v>71</v>
       </c>
       <c r="L30" s="73"/>
       <c r="M30" s="76"/>
@@ -8090,10 +8104,10 @@
       <c r="A31" s="80"/>
       <c r="B31" s="46"/>
       <c r="C31" s="112"/>
-      <c r="D31" s="208" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" s="209"/>
+      <c r="D31" s="240" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="241"/>
       <c r="F31" s="135" t="s">
         <v>162</v>
       </c>
@@ -8117,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="128" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N31" s="122">
         <v>30</v>
@@ -8133,16 +8147,16 @@
       <c r="X31"/>
       <c r="Y31"/>
     </row>
-    <row r="32" spans="1:25" ht="24.95" customHeight="1">
+    <row r="32" spans="1:25" ht="25" customHeight="1">
       <c r="A32" s="80"/>
       <c r="B32" s="46"/>
       <c r="C32" s="112"/>
-      <c r="D32" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="205"/>
+      <c r="D32" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="213"/>
       <c r="F32" s="132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G32" s="134">
         <v>0</v>
@@ -8177,18 +8191,18 @@
       <c r="A33" s="80"/>
       <c r="B33" s="46"/>
       <c r="C33" s="118" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="196" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="271"/>
-      <c r="F33" s="271"/>
-      <c r="G33" s="271"/>
-      <c r="H33" s="271"/>
-      <c r="I33" s="271"/>
-      <c r="J33" s="271"/>
-      <c r="K33" s="271"/>
+        <v>63</v>
+      </c>
+      <c r="D33" s="212" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="215"/>
+      <c r="F33" s="215"/>
+      <c r="G33" s="215"/>
+      <c r="H33" s="215"/>
+      <c r="I33" s="215"/>
+      <c r="J33" s="215"/>
+      <c r="K33" s="215"/>
       <c r="L33" s="74"/>
       <c r="M33" s="69"/>
       <c r="N33" s="72"/>
@@ -8203,29 +8217,29 @@
       <c r="X33"/>
       <c r="Y33"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1">
+    <row r="34" spans="1:25" ht="20.149999999999999" customHeight="1">
       <c r="A34" s="80"/>
       <c r="B34" s="46"/>
       <c r="C34" s="118"/>
-      <c r="D34" s="207"/>
-      <c r="E34" s="207"/>
+      <c r="D34" s="204"/>
+      <c r="E34" s="204"/>
       <c r="F34" s="120" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G34" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" s="120" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="H34" s="120" t="s">
+      <c r="J34" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="I34" s="120" t="s">
+      <c r="K34" s="120" t="s">
         <v>69</v>
-      </c>
-      <c r="J34" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="K34" s="120" t="s">
-        <v>71</v>
       </c>
       <c r="L34" s="67"/>
       <c r="M34" s="69"/>
@@ -8248,23 +8262,23 @@
       <c r="D35" s="210" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="203"/>
-      <c r="F35" s="160" t="s">
+      <c r="E35" s="211"/>
+      <c r="F35" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="G35" s="164" t="s">
+      <c r="G35" s="156" t="s">
         <v>169</v>
       </c>
-      <c r="H35" s="164" t="s">
+      <c r="H35" s="156" t="s">
         <v>170</v>
       </c>
-      <c r="I35" s="164" t="s">
+      <c r="I35" s="156" t="s">
         <v>171</v>
       </c>
-      <c r="J35" s="164" t="s">
+      <c r="J35" s="156" t="s">
         <v>172</v>
       </c>
-      <c r="K35" s="164" t="s">
+      <c r="K35" s="156" t="s">
         <v>173</v>
       </c>
       <c r="L35" s="67">
@@ -8272,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="75" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N35" s="68">
         <v>20</v>
@@ -8289,16 +8303,16 @@
       <c r="X35"/>
       <c r="Y35"/>
     </row>
-    <row r="36" spans="1:25" ht="24.95" customHeight="1">
+    <row r="36" spans="1:25" ht="25" customHeight="1">
       <c r="A36" s="80"/>
       <c r="B36" s="55"/>
       <c r="C36" s="112"/>
-      <c r="D36" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" s="205"/>
+      <c r="D36" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="213"/>
       <c r="F36" s="132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G36" s="134">
         <v>0</v>
@@ -8334,18 +8348,18 @@
       <c r="A37" s="80"/>
       <c r="B37" s="55"/>
       <c r="C37" s="118" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="206" t="s">
-        <v>87</v>
-      </c>
-      <c r="E37" s="271"/>
-      <c r="F37" s="271"/>
-      <c r="G37" s="271"/>
-      <c r="H37" s="271"/>
-      <c r="I37" s="271"/>
-      <c r="J37" s="271"/>
-      <c r="K37" s="271"/>
+        <v>84</v>
+      </c>
+      <c r="D37" s="246" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="215"/>
+      <c r="F37" s="215"/>
+      <c r="G37" s="215"/>
+      <c r="H37" s="215"/>
+      <c r="I37" s="215"/>
+      <c r="J37" s="215"/>
+      <c r="K37" s="215"/>
       <c r="L37" s="67"/>
       <c r="M37" s="69"/>
       <c r="N37" s="68"/>
@@ -8361,29 +8375,29 @@
       <c r="X37"/>
       <c r="Y37"/>
     </row>
-    <row r="38" spans="1:25" ht="24.95" customHeight="1">
+    <row r="38" spans="1:25" ht="25" customHeight="1">
       <c r="A38" s="80"/>
       <c r="B38" s="55"/>
       <c r="C38" s="118"/>
-      <c r="D38" s="207"/>
-      <c r="E38" s="207"/>
+      <c r="D38" s="204"/>
+      <c r="E38" s="204"/>
       <c r="F38" s="120" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="120" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="G38" s="120" t="s">
+      <c r="I38" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="120" t="s">
+      <c r="J38" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="I38" s="120" t="s">
+      <c r="K38" s="120" t="s">
         <v>26</v>
-      </c>
-      <c r="J38" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="K38" s="120" t="s">
-        <v>28</v>
       </c>
       <c r="L38" s="67"/>
       <c r="M38" s="69"/>
@@ -8404,23 +8418,23 @@
       <c r="A39" s="80"/>
       <c r="B39" s="57"/>
       <c r="C39" s="112"/>
-      <c r="D39" s="208" t="s">
-        <v>88</v>
-      </c>
-      <c r="E39" s="208"/>
+      <c r="D39" s="240" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" s="240"/>
       <c r="F39" s="135" t="s">
         <v>160</v>
       </c>
       <c r="G39" s="145" t="s">
         <v>174</v>
       </c>
-      <c r="H39" s="165" t="s">
+      <c r="H39" s="157" t="s">
         <v>175</v>
       </c>
       <c r="I39" s="137" t="s">
         <v>176</v>
       </c>
-      <c r="J39" s="165" t="s">
+      <c r="J39" s="157" t="s">
         <v>177</v>
       </c>
       <c r="K39" s="138" t="s">
@@ -8431,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="70" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N39" s="68">
         <v>15</v>
@@ -8448,16 +8462,16 @@
       <c r="X39"/>
       <c r="Y39"/>
     </row>
-    <row r="40" spans="1:25" ht="24.95" customHeight="1">
+    <row r="40" spans="1:25" ht="25" customHeight="1">
       <c r="A40" s="80"/>
       <c r="B40" s="57"/>
       <c r="C40" s="112"/>
-      <c r="D40" s="204" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="205"/>
+      <c r="D40" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="213"/>
       <c r="F40" s="132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G40" s="134">
         <v>0</v>
@@ -8489,7 +8503,7 @@
       <c r="X40"/>
       <c r="Y40"/>
     </row>
-    <row r="41" spans="1:25" ht="24.95" customHeight="1">
+    <row r="41" spans="1:25" ht="25" customHeight="1">
       <c r="A41" s="80"/>
       <c r="B41" s="59"/>
       <c r="D41" s="64"/>
@@ -8499,17 +8513,17 @@
       <c r="H41" s="65"/>
       <c r="I41" s="65"/>
       <c r="J41" s="65"/>
-      <c r="K41" s="192" t="s">
-        <v>95</v>
-      </c>
-      <c r="L41" s="193">
+      <c r="K41" s="257" t="s">
+        <v>93</v>
+      </c>
+      <c r="L41" s="258">
         <f>SUM(L15:L40)</f>
         <v>0</v>
       </c>
-      <c r="M41" s="194" t="s">
-        <v>36</v>
-      </c>
-      <c r="N41" s="200">
+      <c r="M41" s="259" t="s">
+        <v>34</v>
+      </c>
+      <c r="N41" s="242">
         <f>SUM(N15:N40)</f>
         <v>100</v>
       </c>
@@ -8524,7 +8538,7 @@
       <c r="X41"/>
       <c r="Y41"/>
     </row>
-    <row r="42" spans="1:25" ht="24.95" customHeight="1">
+    <row r="42" spans="1:25" ht="25" customHeight="1">
       <c r="A42" s="80"/>
       <c r="B42" s="59"/>
       <c r="D42" s="64"/>
@@ -8534,10 +8548,10 @@
       <c r="H42" s="65"/>
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
-      <c r="K42" s="192"/>
-      <c r="L42" s="193"/>
-      <c r="M42" s="195"/>
-      <c r="N42" s="200"/>
+      <c r="K42" s="257"/>
+      <c r="L42" s="258"/>
+      <c r="M42" s="260"/>
+      <c r="N42" s="242"/>
       <c r="O42" s="80"/>
       <c r="Q42"/>
       <c r="R42"/>
@@ -8569,11 +8583,11 @@
     <row r="44" spans="1:25" ht="30.75" customHeight="1">
       <c r="A44" s="80"/>
       <c r="B44" s="114"/>
-      <c r="C44" s="272" t="s">
-        <v>96</v>
-      </c>
-      <c r="D44" s="272"/>
-      <c r="E44" s="272"/>
+      <c r="C44" s="243" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="243"/>
+      <c r="E44" s="243"/>
       <c r="F44" s="81"/>
       <c r="G44" s="81"/>
       <c r="H44" s="81"/>
@@ -8589,23 +8603,23 @@
       <c r="A45" s="80"/>
       <c r="B45" s="104"/>
       <c r="C45" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="84" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="244" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="84" t="s">
-        <v>98</v>
-      </c>
-      <c r="E45" s="201" t="s">
-        <v>99</v>
-      </c>
-      <c r="F45" s="201"/>
-      <c r="G45" s="201"/>
-      <c r="H45" s="201"/>
-      <c r="I45" s="201"/>
+      <c r="F45" s="244"/>
+      <c r="G45" s="244"/>
+      <c r="H45" s="244"/>
+      <c r="I45" s="244"/>
       <c r="J45" s="85"/>
       <c r="K45" s="84"/>
       <c r="L45" s="84"/>
       <c r="M45" s="86" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N45" s="83"/>
       <c r="O45" s="80"/>
@@ -8614,20 +8628,20 @@
       <c r="A46" s="80"/>
       <c r="B46" s="114"/>
       <c r="C46" s="87" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" s="88" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="250" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="E46" s="197" t="s">
-        <v>103</v>
-      </c>
-      <c r="F46" s="197"/>
-      <c r="G46" s="197"/>
-      <c r="H46" s="197"/>
-      <c r="I46" s="197"/>
-      <c r="J46" s="197"/>
-      <c r="K46" s="197"/>
+      <c r="F46" s="250"/>
+      <c r="G46" s="250"/>
+      <c r="H46" s="250"/>
+      <c r="I46" s="250"/>
+      <c r="J46" s="250"/>
+      <c r="K46" s="250"/>
       <c r="L46" s="88"/>
       <c r="M46" s="89">
         <v>3</v>
@@ -8639,20 +8653,20 @@
       <c r="A47" s="80"/>
       <c r="B47" s="104"/>
       <c r="C47" s="90" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>104</v>
-      </c>
-      <c r="E47" s="197" t="s">
-        <v>105</v>
-      </c>
-      <c r="F47" s="197"/>
-      <c r="G47" s="197"/>
-      <c r="H47" s="197"/>
-      <c r="I47" s="197"/>
-      <c r="J47" s="197"/>
-      <c r="K47" s="197"/>
+        <v>102</v>
+      </c>
+      <c r="E47" s="250" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="250"/>
+      <c r="G47" s="250"/>
+      <c r="H47" s="250"/>
+      <c r="I47" s="250"/>
+      <c r="J47" s="250"/>
+      <c r="K47" s="250"/>
       <c r="L47" s="88"/>
       <c r="M47" s="91">
         <v>3</v>
@@ -8664,20 +8678,20 @@
       <c r="A48" s="80"/>
       <c r="B48" s="114"/>
       <c r="C48" s="87" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>106</v>
-      </c>
-      <c r="E48" s="197" t="s">
-        <v>107</v>
-      </c>
-      <c r="F48" s="197"/>
-      <c r="G48" s="197"/>
-      <c r="H48" s="197"/>
-      <c r="I48" s="197"/>
-      <c r="J48" s="197"/>
-      <c r="K48" s="197"/>
+        <v>104</v>
+      </c>
+      <c r="E48" s="250" t="s">
+        <v>105</v>
+      </c>
+      <c r="F48" s="250"/>
+      <c r="G48" s="250"/>
+      <c r="H48" s="250"/>
+      <c r="I48" s="250"/>
+      <c r="J48" s="250"/>
+      <c r="K48" s="250"/>
       <c r="L48" s="88"/>
       <c r="M48" s="89">
         <v>3</v>
@@ -8689,20 +8703,20 @@
       <c r="A49" s="80"/>
       <c r="B49" s="104"/>
       <c r="C49" s="92" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D49" s="93" t="s">
-        <v>109</v>
-      </c>
-      <c r="E49" s="191" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" s="249" t="s">
         <v>179</v>
       </c>
-      <c r="F49" s="191"/>
-      <c r="G49" s="191"/>
-      <c r="H49" s="191"/>
-      <c r="I49" s="191"/>
-      <c r="J49" s="191"/>
-      <c r="K49" s="191"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="249"/>
+      <c r="H49" s="249"/>
+      <c r="I49" s="249"/>
+      <c r="J49" s="249"/>
+      <c r="K49" s="249"/>
       <c r="L49" s="93"/>
       <c r="M49" s="94">
         <v>3</v>
@@ -8714,20 +8728,20 @@
       <c r="A50" s="80"/>
       <c r="B50" s="114"/>
       <c r="C50" s="95" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D50" s="96" t="s">
-        <v>111</v>
-      </c>
-      <c r="E50" s="198" t="s">
-        <v>112</v>
-      </c>
-      <c r="F50" s="198"/>
-      <c r="G50" s="198"/>
-      <c r="H50" s="198"/>
-      <c r="I50" s="198"/>
-      <c r="J50" s="198"/>
-      <c r="K50" s="198"/>
+        <v>109</v>
+      </c>
+      <c r="E50" s="248" t="s">
+        <v>110</v>
+      </c>
+      <c r="F50" s="248"/>
+      <c r="G50" s="248"/>
+      <c r="H50" s="248"/>
+      <c r="I50" s="248"/>
+      <c r="J50" s="248"/>
+      <c r="K50" s="248"/>
       <c r="L50" s="96"/>
       <c r="M50" s="97">
         <v>3</v>
@@ -8739,20 +8753,20 @@
       <c r="A51" s="80"/>
       <c r="B51" s="115"/>
       <c r="C51" s="98" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="93" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="191" t="s">
-        <v>115</v>
-      </c>
-      <c r="F51" s="191"/>
-      <c r="G51" s="191"/>
-      <c r="H51" s="191"/>
-      <c r="I51" s="191"/>
-      <c r="J51" s="191"/>
-      <c r="K51" s="191"/>
+      <c r="F51" s="249"/>
+      <c r="G51" s="249"/>
+      <c r="H51" s="249"/>
+      <c r="I51" s="249"/>
+      <c r="J51" s="249"/>
+      <c r="K51" s="249"/>
       <c r="L51" s="93"/>
       <c r="M51" s="99">
         <v>3</v>
@@ -8764,20 +8778,20 @@
       <c r="A52" s="80"/>
       <c r="B52" s="104"/>
       <c r="C52" s="101" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D52" s="96" t="s">
-        <v>117</v>
-      </c>
-      <c r="E52" s="198" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" s="248" t="s">
         <v>180</v>
       </c>
-      <c r="F52" s="198"/>
-      <c r="G52" s="198"/>
-      <c r="H52" s="198"/>
-      <c r="I52" s="198"/>
-      <c r="J52" s="198"/>
-      <c r="K52" s="198"/>
+      <c r="F52" s="248"/>
+      <c r="G52" s="248"/>
+      <c r="H52" s="248"/>
+      <c r="I52" s="248"/>
+      <c r="J52" s="248"/>
+      <c r="K52" s="248"/>
       <c r="L52" s="96"/>
       <c r="M52" s="102">
         <v>3</v>
@@ -8789,20 +8803,20 @@
       <c r="A53" s="80"/>
       <c r="B53" s="104"/>
       <c r="C53" s="92" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D53" s="93" t="s">
-        <v>119</v>
-      </c>
-      <c r="E53" s="191" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" s="249" t="s">
         <v>181</v>
       </c>
-      <c r="F53" s="191"/>
-      <c r="G53" s="191"/>
-      <c r="H53" s="191"/>
-      <c r="I53" s="191"/>
-      <c r="J53" s="191"/>
-      <c r="K53" s="191"/>
+      <c r="F53" s="249"/>
+      <c r="G53" s="249"/>
+      <c r="H53" s="249"/>
+      <c r="I53" s="249"/>
+      <c r="J53" s="249"/>
+      <c r="K53" s="249"/>
       <c r="L53" s="93"/>
       <c r="M53" s="94">
         <v>3</v>
@@ -8814,20 +8828,20 @@
       <c r="A54" s="80"/>
       <c r="B54" s="104"/>
       <c r="C54" s="95" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="D54" s="96" t="s">
-        <v>121</v>
-      </c>
-      <c r="E54" s="198" t="s">
+      <c r="E54" s="248" t="s">
         <v>182</v>
       </c>
-      <c r="F54" s="198"/>
-      <c r="G54" s="198"/>
-      <c r="H54" s="198"/>
-      <c r="I54" s="198"/>
-      <c r="J54" s="198"/>
-      <c r="K54" s="198"/>
+      <c r="F54" s="248"/>
+      <c r="G54" s="248"/>
+      <c r="H54" s="248"/>
+      <c r="I54" s="248"/>
+      <c r="J54" s="248"/>
+      <c r="K54" s="248"/>
       <c r="L54" s="96"/>
       <c r="M54" s="97">
         <v>3</v>
@@ -8839,20 +8853,20 @@
       <c r="A55" s="80"/>
       <c r="B55" s="116"/>
       <c r="C55" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D55" s="93" t="s">
+        <v>122</v>
+      </c>
+      <c r="E55" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="D55" s="93" t="s">
-        <v>124</v>
-      </c>
-      <c r="E55" s="191" t="s">
-        <v>125</v>
-      </c>
-      <c r="F55" s="191"/>
-      <c r="G55" s="191"/>
-      <c r="H55" s="191"/>
-      <c r="I55" s="191"/>
-      <c r="J55" s="191"/>
-      <c r="K55" s="191"/>
+      <c r="F55" s="249"/>
+      <c r="G55" s="249"/>
+      <c r="H55" s="249"/>
+      <c r="I55" s="249"/>
+      <c r="J55" s="249"/>
+      <c r="K55" s="249"/>
       <c r="L55" s="93"/>
       <c r="M55" s="99">
         <v>3</v>
@@ -8864,20 +8878,20 @@
       <c r="A56" s="80"/>
       <c r="B56" s="114"/>
       <c r="C56" s="101" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D56" s="96" t="s">
-        <v>126</v>
-      </c>
-      <c r="E56" s="198" t="s">
+        <v>124</v>
+      </c>
+      <c r="E56" s="248" t="s">
         <v>183</v>
       </c>
-      <c r="F56" s="198"/>
-      <c r="G56" s="198"/>
-      <c r="H56" s="198"/>
-      <c r="I56" s="198"/>
-      <c r="J56" s="198"/>
-      <c r="K56" s="198"/>
+      <c r="F56" s="248"/>
+      <c r="G56" s="248"/>
+      <c r="H56" s="248"/>
+      <c r="I56" s="248"/>
+      <c r="J56" s="248"/>
+      <c r="K56" s="248"/>
       <c r="L56" s="96"/>
       <c r="M56" s="102">
         <v>3</v>
@@ -8922,252 +8936,252 @@
     <row r="59" spans="1:15" ht="24" customHeight="1">
       <c r="A59" s="80"/>
       <c r="B59" s="117" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="272" t="s">
-        <v>129</v>
-      </c>
-      <c r="D59" s="272"/>
-      <c r="E59" s="272"/>
+        <v>126</v>
+      </c>
+      <c r="C59" s="243" t="s">
+        <v>127</v>
+      </c>
+      <c r="D59" s="243"/>
+      <c r="E59" s="243"/>
       <c r="F59" s="105" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L59" s="104"/>
       <c r="M59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N59" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O59" s="80"/>
     </row>
     <row r="60" spans="1:15" ht="15.75" customHeight="1">
       <c r="A60" s="80"/>
       <c r="B60" s="117" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60" s="106" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="D60" s="106" t="s">
+        <v>129</v>
+      </c>
+      <c r="E60" s="247" t="s">
         <v>130</v>
       </c>
-      <c r="D60" s="106" t="s">
+      <c r="F60" s="247"/>
+      <c r="G60" s="247"/>
+      <c r="H60" s="247"/>
+      <c r="I60" s="107" t="s">
         <v>131</v>
-      </c>
-      <c r="E60" s="199" t="s">
-        <v>132</v>
-      </c>
-      <c r="F60" s="199"/>
-      <c r="G60" s="199"/>
-      <c r="H60" s="199"/>
-      <c r="I60" s="107" t="s">
-        <v>133</v>
       </c>
       <c r="J60" s="106"/>
       <c r="K60" s="106"/>
       <c r="L60" s="106"/>
       <c r="M60" s="106"/>
       <c r="N60" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O60" s="80"/>
     </row>
     <row r="61" spans="1:15" ht="48.75" customHeight="1">
       <c r="A61" s="80"/>
       <c r="B61" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C61" s="108">
         <v>1</v>
       </c>
       <c r="D61" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="E61" s="253" t="s">
+        <v>133</v>
+      </c>
+      <c r="F61" s="253"/>
+      <c r="G61" s="253"/>
+      <c r="H61" s="253"/>
+      <c r="I61" s="254" t="s">
         <v>134</v>
       </c>
-      <c r="E61" s="186" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61" s="186"/>
-      <c r="G61" s="186"/>
-      <c r="H61" s="186"/>
-      <c r="I61" s="187" t="s">
-        <v>136</v>
-      </c>
-      <c r="J61" s="187"/>
-      <c r="K61" s="187"/>
-      <c r="L61" s="187"/>
-      <c r="M61" s="187"/>
+      <c r="J61" s="254"/>
+      <c r="K61" s="254"/>
+      <c r="L61" s="254"/>
+      <c r="M61" s="254"/>
       <c r="N61" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O61" s="80"/>
     </row>
     <row r="62" spans="1:15" ht="47.25" customHeight="1">
       <c r="A62" s="80"/>
       <c r="B62" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C62" s="110">
         <v>2</v>
       </c>
       <c r="D62" s="111" t="s">
+        <v>135</v>
+      </c>
+      <c r="E62" s="251" t="s">
+        <v>136</v>
+      </c>
+      <c r="F62" s="251"/>
+      <c r="G62" s="251"/>
+      <c r="H62" s="251"/>
+      <c r="I62" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="184" t="s">
-        <v>138</v>
-      </c>
-      <c r="F62" s="184"/>
-      <c r="G62" s="184"/>
-      <c r="H62" s="184"/>
-      <c r="I62" s="185" t="s">
-        <v>139</v>
-      </c>
-      <c r="J62" s="185"/>
-      <c r="K62" s="185"/>
-      <c r="L62" s="185"/>
-      <c r="M62" s="185"/>
+      <c r="J62" s="252"/>
+      <c r="K62" s="252"/>
+      <c r="L62" s="252"/>
+      <c r="M62" s="252"/>
       <c r="N62" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O62" s="80"/>
     </row>
     <row r="63" spans="1:15" ht="42" customHeight="1">
       <c r="A63" s="80"/>
       <c r="B63" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C63" s="108">
         <v>3</v>
       </c>
       <c r="D63" s="109" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" s="253" t="s">
+        <v>139</v>
+      </c>
+      <c r="F63" s="253"/>
+      <c r="G63" s="253"/>
+      <c r="H63" s="253"/>
+      <c r="I63" s="254" t="s">
         <v>140</v>
       </c>
-      <c r="E63" s="186" t="s">
-        <v>141</v>
-      </c>
-      <c r="F63" s="186"/>
-      <c r="G63" s="186"/>
-      <c r="H63" s="186"/>
-      <c r="I63" s="187" t="s">
-        <v>142</v>
-      </c>
-      <c r="J63" s="187"/>
-      <c r="K63" s="187"/>
-      <c r="L63" s="187"/>
-      <c r="M63" s="187"/>
+      <c r="J63" s="254"/>
+      <c r="K63" s="254"/>
+      <c r="L63" s="254"/>
+      <c r="M63" s="254"/>
       <c r="N63" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O63" s="80"/>
     </row>
     <row r="64" spans="1:15" ht="42" customHeight="1">
       <c r="A64" s="80"/>
       <c r="B64" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C64" s="110">
         <v>4</v>
       </c>
       <c r="D64" s="111" t="s">
+        <v>141</v>
+      </c>
+      <c r="E64" s="251" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="251"/>
+      <c r="G64" s="251"/>
+      <c r="H64" s="251"/>
+      <c r="I64" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="E64" s="184" t="s">
-        <v>144</v>
-      </c>
-      <c r="F64" s="184"/>
-      <c r="G64" s="184"/>
-      <c r="H64" s="184"/>
-      <c r="I64" s="185" t="s">
-        <v>145</v>
-      </c>
-      <c r="J64" s="185"/>
-      <c r="K64" s="185"/>
-      <c r="L64" s="185"/>
-      <c r="M64" s="185"/>
+      <c r="J64" s="252"/>
+      <c r="K64" s="252"/>
+      <c r="L64" s="252"/>
+      <c r="M64" s="252"/>
       <c r="N64" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O64" s="80"/>
     </row>
     <row r="65" spans="1:15" ht="36" customHeight="1">
       <c r="A65" s="80"/>
       <c r="B65" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C65" s="108">
         <v>5</v>
       </c>
       <c r="D65" s="109" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" s="253" t="s">
+        <v>145</v>
+      </c>
+      <c r="F65" s="253"/>
+      <c r="G65" s="253"/>
+      <c r="H65" s="253"/>
+      <c r="I65" s="254" t="s">
         <v>146</v>
       </c>
-      <c r="E65" s="186" t="s">
-        <v>147</v>
-      </c>
-      <c r="F65" s="186"/>
-      <c r="G65" s="186"/>
-      <c r="H65" s="186"/>
-      <c r="I65" s="187" t="s">
-        <v>148</v>
-      </c>
-      <c r="J65" s="187"/>
-      <c r="K65" s="187"/>
-      <c r="L65" s="187"/>
-      <c r="M65" s="187"/>
+      <c r="J65" s="254"/>
+      <c r="K65" s="254"/>
+      <c r="L65" s="254"/>
+      <c r="M65" s="254"/>
       <c r="N65" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O65" s="80"/>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1">
       <c r="A66" s="80"/>
       <c r="B66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L66" s="104"/>
       <c r="M66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N66" s="104" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O66" s="80"/>
     </row>
@@ -10146,43 +10160,33 @@
     <protectedRange algorithmName="SHA-512" hashValue="NcQe0VjxFnxU9SziGkmWOoYUYoQ0T62vv+WqFE1sowJD2+jDiq1RKEMS6wObDPCk433k/JG1CTU3j62rwNOzdg==" saltValue="OlYFZTFPx5QDCqKlqXj8fw==" spinCount="100000" sqref="G39" name="Range1_2_1_7"/>
   </protectedRanges>
   <mergeCells count="80">
-    <mergeCell ref="E54:K54"/>
-    <mergeCell ref="D21:K21"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="E46:K46"/>
-    <mergeCell ref="E47:K47"/>
-    <mergeCell ref="E48:K48"/>
-    <mergeCell ref="E49:K49"/>
-    <mergeCell ref="E50:K50"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="E52:K52"/>
-    <mergeCell ref="E53:K53"/>
-    <mergeCell ref="N3:N7"/>
-    <mergeCell ref="C10:M10"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="M3:M7"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="L3:L7"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F3:K7"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:M65"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D37:K37"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D33:K33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="L41:L42"/>
+    <mergeCell ref="M41:M42"/>
+    <mergeCell ref="I62:M62"/>
     <mergeCell ref="E63:H63"/>
     <mergeCell ref="I63:M63"/>
     <mergeCell ref="E64:H64"/>
@@ -10199,152 +10203,162 @@
     <mergeCell ref="I61:M61"/>
     <mergeCell ref="C59:E59"/>
     <mergeCell ref="E51:K51"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="I65:M65"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D37:K37"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="L41:L42"/>
-    <mergeCell ref="M41:M42"/>
-    <mergeCell ref="I62:M62"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="M3:M7"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="L3:L7"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F3:K7"/>
+    <mergeCell ref="N3:N7"/>
+    <mergeCell ref="C10:M10"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D17:K17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="E52:K52"/>
+    <mergeCell ref="E53:K53"/>
+    <mergeCell ref="E54:K54"/>
+    <mergeCell ref="D21:K21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="E46:K46"/>
+    <mergeCell ref="E47:K47"/>
+    <mergeCell ref="E48:K48"/>
+    <mergeCell ref="E49:K49"/>
+    <mergeCell ref="E50:K50"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G26:I26"/>
   </mergeCells>
   <conditionalFormatting sqref="L15 L27">
-    <cfRule type="cellIs" dxfId="41" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="66" operator="equal">
+      <formula>"INSUFFICIENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="65" operator="equal">
+      <formula>"SUFFICIENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="64" operator="equal">
+      <formula>"GOOD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="63" operator="equal">
+      <formula>"EXCELLENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="68" operator="equal">
       <formula>"POOR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="67" operator="equal">
       <formula>"MISSING"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="66" operator="equal">
-      <formula>"INSUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="65" operator="equal">
-      <formula>"SUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="64" operator="equal">
-      <formula>"GOOD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="63" operator="equal">
-      <formula>"EXCELLENT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="35" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
+      <formula>"MISSING"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
       <formula>"EXCELLENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="9" operator="equal">
       <formula>"GOOD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="10" operator="equal">
       <formula>"SUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
       <formula>"INSUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="12" operator="equal">
-      <formula>"MISSING"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="30" priority="13" operator="equal">
       <formula>"POOR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23">
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
-      <formula>"EXCELLENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
       <formula>"GOOD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
       <formula>"SUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="5" operator="equal">
       <formula>"INSUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
       <formula>"MISSING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="7" operator="equal">
       <formula>"POOR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+      <formula>"EXCELLENT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L31">
     <cfRule type="cellIs" dxfId="23" priority="42" operator="equal">
       <formula>"EXCELLENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
-      <formula>"POOR"</formula>
+    <cfRule type="cellIs" dxfId="22" priority="43" operator="equal">
+      <formula>"GOOD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="46" operator="equal">
-      <formula>"MISSING"</formula>
+    <cfRule type="cellIs" dxfId="21" priority="44" operator="equal">
+      <formula>"SUFFICIENT"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="20" priority="45" operator="equal">
       <formula>"INSUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="44" operator="equal">
-      <formula>"SUFFICIENT"</formula>
+    <cfRule type="cellIs" dxfId="19" priority="47" operator="equal">
+      <formula>"POOR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="43" operator="equal">
-      <formula>"GOOD"</formula>
+    <cfRule type="cellIs" dxfId="18" priority="46" operator="equal">
+      <formula>"MISSING"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35">
-    <cfRule type="cellIs" dxfId="17" priority="36" operator="equal">
-      <formula>"EXCELLENT"</formula>
+    <cfRule type="cellIs" dxfId="17" priority="37" operator="equal">
+      <formula>"GOOD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="38" operator="equal">
+      <formula>"SUFFICIENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="39" operator="equal">
+      <formula>"INSUFFICIENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="40" operator="equal">
       <formula>"MISSING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="41" operator="equal">
       <formula>"POOR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="39" operator="equal">
-      <formula>"INSUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="38" operator="equal">
-      <formula>"SUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="37" operator="equal">
-      <formula>"GOOD"</formula>
+    <cfRule type="cellIs" dxfId="12" priority="36" operator="equal">
+      <formula>"EXCELLENT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L39">
-    <cfRule type="cellIs" dxfId="11" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="30" operator="equal">
+      <formula>"EXCELLENT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="31" operator="equal">
+      <formula>"GOOD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="35" operator="equal">
       <formula>"POOR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="34" operator="equal">
       <formula>"MISSING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="33" operator="equal">
       <formula>"INSUFFICIENT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="32" operator="equal">
       <formula>"SUFFICIENT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="31" operator="equal">
-      <formula>"GOOD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="30" operator="equal">
-      <formula>"EXCELLENT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3">
@@ -10362,11 +10376,11 @@
     <cfRule type="expression" dxfId="2" priority="14" stopIfTrue="1">
       <formula>$L$3&gt;5.5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="15" stopIfTrue="1">
+      <formula>($L$3&lt;5.5) &amp; ($L$3&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="16" stopIfTrue="1">
       <formula>$L$3=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="15" stopIfTrue="1">
-      <formula>($L$3&lt;5.5) &amp; ($L$3&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
@@ -10401,139 +10415,139 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2B1E53-A545-453F-B7B9-0A7D0122D722}">
   <dimension ref="B1:F10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.95"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="3" max="3" width="69.7109375" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="69.7265625" customWidth="1"/>
+    <col min="4" max="4" width="28.26953125" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="260" t="s">
+      <c r="B1" s="266" t="s">
         <v>184</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
+      <c r="C1" s="266"/>
+      <c r="D1" s="266"/>
+      <c r="E1" s="266"/>
+      <c r="F1" s="266"/>
     </row>
     <row r="2" spans="2:6">
-      <c r="B2" s="260"/>
-      <c r="C2" s="260"/>
-      <c r="D2" s="260"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="260"/>
-    </row>
-    <row r="3" spans="2:6" ht="27">
-      <c r="B3" s="180" t="s">
+      <c r="B2" s="266"/>
+      <c r="C2" s="266"/>
+      <c r="D2" s="266"/>
+      <c r="E2" s="266"/>
+      <c r="F2" s="266"/>
+    </row>
+    <row r="3" spans="2:6" ht="25">
+      <c r="B3" s="172" t="s">
         <v>185</v>
       </c>
-      <c r="C3" s="171" t="s">
+      <c r="C3" s="163" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="182" t="s">
+      <c r="D3" s="174" t="s">
         <v>187</v>
       </c>
-      <c r="E3" s="181"/>
-      <c r="F3" s="183" t="s">
+      <c r="E3" s="173"/>
+      <c r="F3" s="175" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="20.100000000000001">
-      <c r="B4" s="180">
+    <row r="4" spans="2:6" ht="20">
+      <c r="B4" s="172">
         <v>0</v>
       </c>
-      <c r="C4" s="172" t="s">
+      <c r="C4" s="164" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="173">
+      <c r="D4" s="165">
         <v>0.15</v>
       </c>
-      <c r="F4" s="173">
+      <c r="F4" s="165">
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="20.100000000000001">
-      <c r="B5" s="180">
+    <row r="5" spans="2:6" ht="20">
+      <c r="B5" s="172">
         <v>1</v>
       </c>
-      <c r="C5" s="172" t="s">
+      <c r="C5" s="164" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="173">
+      <c r="D5" s="165">
         <v>0.1</v>
       </c>
-      <c r="F5" s="173">
+      <c r="F5" s="165">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="20.100000000000001">
-      <c r="B6" s="180">
+    <row r="6" spans="2:6" ht="20">
+      <c r="B6" s="172">
         <v>2</v>
       </c>
-      <c r="C6" s="172" t="s">
+      <c r="C6" s="164" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="173">
+      <c r="D6" s="165">
         <v>0.1</v>
       </c>
-      <c r="F6" s="173">
+      <c r="F6" s="165">
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="20.100000000000001">
-      <c r="B7" s="180">
+    <row r="7" spans="2:6" ht="20">
+      <c r="B7" s="172">
         <v>6</v>
       </c>
-      <c r="C7" s="172" t="s">
+      <c r="C7" s="164" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="173">
+      <c r="D7" s="165">
         <v>0.1</v>
       </c>
-      <c r="F7" s="173">
+      <c r="F7" s="165">
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="20.100000000000001">
-      <c r="B8" s="180">
+    <row r="8" spans="2:6" ht="20">
+      <c r="B8" s="172">
         <v>8</v>
       </c>
-      <c r="C8" s="172" t="s">
+      <c r="C8" s="164" t="s">
         <v>193</v>
       </c>
-      <c r="D8" s="174">
+      <c r="D8" s="166">
         <v>0.15</v>
       </c>
-      <c r="F8" s="174">
+      <c r="F8" s="166">
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="20.100000000000001">
-      <c r="B9" s="180">
+    <row r="9" spans="2:6" ht="20">
+      <c r="B9" s="172">
         <v>8</v>
       </c>
-      <c r="C9" s="172" t="s">
+      <c r="C9" s="164" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="174">
+      <c r="D9" s="166">
         <v>0.15</v>
       </c>
-      <c r="F9" s="174">
+      <c r="F9" s="166">
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="20.100000000000001">
-      <c r="B10" s="180">
+    <row r="10" spans="2:6" ht="20">
+      <c r="B10" s="172">
         <v>11</v>
       </c>
-      <c r="C10" s="172" t="s">
+      <c r="C10" s="164" t="s">
         <v>195</v>
       </c>
-      <c r="D10" s="173">
+      <c r="D10" s="165">
         <v>0.15</v>
       </c>
-      <c r="F10" s="173">
+      <c r="F10" s="165">
         <v>0.15</v>
       </c>
     </row>
@@ -10548,102 +10562,102 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D04355B-7FF1-4091-B210-DC311C3655BB}">
   <dimension ref="C6:Z38"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.95"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="6" spans="3:26" ht="15.95">
-      <c r="C6" s="146" t="s">
+    <row r="6" spans="3:26" ht="16">
+      <c r="C6" s="176" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="273" t="s">
+      <c r="D6" s="267" t="s">
         <v>185</v>
       </c>
-      <c r="E6" s="274"/>
-      <c r="F6" s="274"/>
-      <c r="G6" s="274"/>
-      <c r="H6" s="274"/>
-      <c r="I6" s="274"/>
-      <c r="J6" s="274"/>
-      <c r="K6" s="274"/>
-      <c r="L6" s="274"/>
-      <c r="M6" s="274"/>
-      <c r="N6" s="274"/>
-      <c r="O6" s="275"/>
-    </row>
-    <row r="7" spans="3:26" ht="15.95">
-      <c r="C7" s="146" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="147">
+      <c r="E6" s="268"/>
+      <c r="F6" s="268"/>
+      <c r="G6" s="268"/>
+      <c r="H6" s="268"/>
+      <c r="I6" s="268"/>
+      <c r="J6" s="268"/>
+      <c r="K6" s="268"/>
+      <c r="L6" s="268"/>
+      <c r="M6" s="268"/>
+      <c r="N6" s="268"/>
+      <c r="O6" s="269"/>
+    </row>
+    <row r="7" spans="3:26" ht="16">
+      <c r="C7" s="176" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="177">
         <v>1</v>
       </c>
-      <c r="E7" s="147">
+      <c r="E7" s="177">
         <v>2</v>
       </c>
-      <c r="F7" s="147">
+      <c r="F7" s="177">
         <v>3</v>
       </c>
-      <c r="G7" s="148">
+      <c r="G7" s="178">
         <v>4</v>
       </c>
-      <c r="H7" s="147">
+      <c r="H7" s="177">
         <v>5</v>
       </c>
-      <c r="I7" s="147">
+      <c r="I7" s="177">
         <v>6</v>
       </c>
-      <c r="J7" s="147">
+      <c r="J7" s="177">
         <v>7</v>
       </c>
-      <c r="K7" s="147">
+      <c r="K7" s="177">
         <v>8</v>
       </c>
-      <c r="L7" s="147">
+      <c r="L7" s="177">
         <v>9</v>
       </c>
-      <c r="M7" s="147">
+      <c r="M7" s="177">
         <v>10</v>
       </c>
-      <c r="N7" s="147">
+      <c r="N7" s="177">
         <v>11</v>
       </c>
-      <c r="O7" s="147">
+      <c r="O7" s="177">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:26" ht="15.95">
-      <c r="C8" s="146" t="s">
+    <row r="8" spans="3:26" ht="16">
+      <c r="C8" s="176" t="s">
         <v>197</v>
       </c>
-      <c r="D8" s="147">
+      <c r="D8" s="177">
         <v>10</v>
       </c>
-      <c r="E8" s="147">
+      <c r="E8" s="177">
         <v>10</v>
       </c>
-      <c r="F8" s="147">
+      <c r="F8" s="177">
         <v>15</v>
       </c>
-      <c r="G8" s="147">
+      <c r="G8" s="177">
         <v>15</v>
       </c>
-      <c r="H8" s="147"/>
-      <c r="I8" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="J8" s="147"/>
-      <c r="K8" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="L8" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="M8" s="147">
+      <c r="H8" s="177"/>
+      <c r="I8" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="177"/>
+      <c r="K8" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="L8" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="M8" s="177">
         <v>20</v>
       </c>
-      <c r="N8" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="O8" s="147">
+      <c r="N8" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="O8" s="177">
         <v>30</v>
       </c>
       <c r="P8">
@@ -10654,235 +10668,235 @@
         <v>198</v>
       </c>
     </row>
-    <row r="9" spans="3:26" ht="15.95">
-      <c r="C9" s="155" t="s">
+    <row r="9" spans="3:26" ht="16">
+      <c r="C9" s="179" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="156">
+      <c r="D9" s="180">
         <v>10</v>
       </c>
-      <c r="E9" s="156">
+      <c r="E9" s="180">
         <v>10</v>
       </c>
-      <c r="F9" s="157"/>
-      <c r="G9" s="156" t="s">
-        <v>128</v>
-      </c>
-      <c r="H9" s="156" t="s">
-        <v>128</v>
-      </c>
-      <c r="I9" s="156">
+      <c r="F9" s="149"/>
+      <c r="G9" s="180" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" s="180" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="180">
         <v>15</v>
       </c>
-      <c r="J9" s="156"/>
-      <c r="K9" s="156">
+      <c r="J9" s="180"/>
+      <c r="K9" s="180">
         <v>25</v>
       </c>
-      <c r="L9" s="156" t="s">
-        <v>128</v>
-      </c>
-      <c r="M9" s="156" t="s">
-        <v>128</v>
-      </c>
-      <c r="N9" s="156">
+      <c r="L9" s="180" t="s">
+        <v>126</v>
+      </c>
+      <c r="M9" s="180" t="s">
+        <v>126</v>
+      </c>
+      <c r="N9" s="180">
         <v>15</v>
       </c>
-      <c r="O9" s="156">
+      <c r="O9" s="180">
         <v>25</v>
       </c>
       <c r="P9">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="R9" s="159" t="s">
+      <c r="R9" s="151" t="s">
         <v>200</v>
       </c>
-      <c r="S9" s="159"/>
-      <c r="T9" s="159"/>
-      <c r="U9" s="159"/>
-      <c r="V9" s="159"/>
-      <c r="W9" s="159"/>
-      <c r="X9" s="159"/>
-      <c r="Y9" s="159"/>
-      <c r="Z9" s="159"/>
-    </row>
-    <row r="10" spans="3:26" ht="15.95">
-      <c r="C10" s="146" t="s">
+      <c r="S9" s="151"/>
+      <c r="T9" s="151"/>
+      <c r="U9" s="151"/>
+      <c r="V9" s="151"/>
+      <c r="W9" s="151"/>
+      <c r="X9" s="151"/>
+      <c r="Y9" s="151"/>
+      <c r="Z9" s="151"/>
+    </row>
+    <row r="10" spans="3:26" ht="16">
+      <c r="C10" s="176" t="s">
         <v>201</v>
       </c>
-      <c r="D10" s="147">
+      <c r="D10" s="177">
         <v>10</v>
       </c>
-      <c r="E10" s="147">
+      <c r="E10" s="177">
         <v>10</v>
       </c>
-      <c r="F10" s="147">
+      <c r="F10" s="177">
         <v>15</v>
       </c>
-      <c r="G10" s="147">
+      <c r="G10" s="177">
         <v>10</v>
       </c>
-      <c r="H10" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="I10" s="147">
+      <c r="H10" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="177">
         <v>10</v>
       </c>
-      <c r="J10" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="K10" s="147">
+      <c r="J10" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="K10" s="177">
         <v>30</v>
       </c>
-      <c r="L10" s="147">
+      <c r="L10" s="177">
         <v>15</v>
       </c>
-      <c r="M10" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="N10" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="O10" s="147" t="s">
-        <v>128</v>
+      <c r="M10" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="N10" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="O10" s="177" t="s">
+        <v>126</v>
       </c>
       <c r="P10">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="R10" s="149" t="s">
+      <c r="R10" s="181" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="11" spans="3:26" ht="15.95">
-      <c r="C11" s="146" t="s">
+    <row r="11" spans="3:26" ht="16">
+      <c r="C11" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="D11" s="147">
+      <c r="D11" s="177">
         <v>20</v>
       </c>
-      <c r="E11" s="147">
+      <c r="E11" s="177">
         <v>10</v>
       </c>
-      <c r="F11" s="147">
+      <c r="F11" s="177">
         <v>10</v>
       </c>
-      <c r="G11" s="147">
+      <c r="G11" s="177">
         <v>10</v>
       </c>
-      <c r="H11" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="I11" s="147">
+      <c r="H11" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="177">
         <v>15</v>
       </c>
-      <c r="J11" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="K11" s="147">
+      <c r="J11" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="K11" s="177">
         <v>20</v>
       </c>
-      <c r="L11" s="147">
+      <c r="L11" s="177">
         <v>15</v>
       </c>
-      <c r="M11" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="N11" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="O11" s="147" t="s">
-        <v>128</v>
+      <c r="M11" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="N11" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="O11" s="177" t="s">
+        <v>126</v>
       </c>
       <c r="P11">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="R11" s="149" t="s">
+      <c r="R11" s="181" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="12" spans="3:26" ht="15.95">
-      <c r="C12" s="146" t="s">
+    <row r="12" spans="3:26" ht="16">
+      <c r="C12" s="176" t="s">
         <v>205</v>
       </c>
-      <c r="D12" s="147">
+      <c r="D12" s="177">
         <v>10</v>
       </c>
-      <c r="E12" s="147">
+      <c r="E12" s="177">
         <v>10</v>
       </c>
-      <c r="F12" s="147">
+      <c r="F12" s="177">
         <v>10</v>
       </c>
-      <c r="G12" s="147">
+      <c r="G12" s="177">
         <v>15</v>
       </c>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="J12" s="147">
+      <c r="H12" s="177"/>
+      <c r="I12" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="177">
         <v>20</v>
       </c>
-      <c r="K12" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="L12" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="M12" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="N12" s="147">
+      <c r="K12" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="L12" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="N12" s="177">
         <v>15</v>
       </c>
-      <c r="O12" s="147">
+      <c r="O12" s="177">
         <v>20</v>
       </c>
       <c r="P12">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="R12" s="149" t="s">
+      <c r="R12" s="181" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="3:26" ht="15.95">
-      <c r="C13" s="146" t="s">
+    <row r="13" spans="3:26" ht="16">
+      <c r="C13" s="176" t="s">
         <v>207</v>
       </c>
-      <c r="D13" s="147">
+      <c r="D13" s="177">
         <v>10</v>
       </c>
-      <c r="E13" s="147">
+      <c r="E13" s="177">
         <v>10</v>
       </c>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="H13" s="147">
+      <c r="F13" s="177"/>
+      <c r="G13" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="177">
         <v>20</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="177">
         <v>20</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="177">
         <v>20</v>
       </c>
-      <c r="K13" s="147">
+      <c r="K13" s="177">
         <v>20</v>
       </c>
-      <c r="L13" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="M13" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147" t="s">
-        <v>128</v>
+      <c r="L13" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="N13" s="177"/>
+      <c r="O13" s="177" t="s">
+        <v>126</v>
       </c>
       <c r="P13">
         <f t="shared" si="0"/>
@@ -10892,276 +10906,276 @@
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="3:26" ht="15.95">
-      <c r="C14" s="146" t="s">
+    <row r="14" spans="3:26" ht="16">
+      <c r="C14" s="176" t="s">
         <v>209</v>
       </c>
-      <c r="D14" s="147">
+      <c r="D14" s="177">
         <v>10</v>
       </c>
-      <c r="E14" s="147">
+      <c r="E14" s="177">
         <v>10</v>
       </c>
-      <c r="F14" s="147">
+      <c r="F14" s="177">
         <v>10</v>
       </c>
-      <c r="G14" s="147"/>
-      <c r="H14" s="147">
+      <c r="G14" s="177"/>
+      <c r="H14" s="177">
         <v>15</v>
       </c>
-      <c r="I14" s="147">
+      <c r="I14" s="177">
         <v>20</v>
       </c>
-      <c r="J14" s="147">
+      <c r="J14" s="177">
         <v>15</v>
       </c>
-      <c r="K14" s="147">
+      <c r="K14" s="177">
         <v>20</v>
       </c>
-      <c r="L14" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="M14" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="N14" s="147"/>
-      <c r="O14" s="147" t="s">
-        <v>128</v>
+      <c r="L14" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="N14" s="177"/>
+      <c r="O14" s="177" t="s">
+        <v>126</v>
       </c>
       <c r="P14">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="R14" s="149" t="s">
+      <c r="R14" s="181" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="15" spans="3:26" ht="15.95">
-      <c r="C15" s="146" t="s">
+    <row r="15" spans="3:26" ht="16">
+      <c r="C15" s="176" t="s">
         <v>211</v>
       </c>
-      <c r="D15" s="147">
+      <c r="D15" s="177">
         <v>10</v>
       </c>
-      <c r="E15" s="147">
+      <c r="E15" s="177">
         <v>10</v>
       </c>
-      <c r="F15" s="147">
+      <c r="F15" s="177">
         <v>10</v>
       </c>
-      <c r="G15" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="H15" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="I15" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="J15" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="K15" s="147">
+      <c r="G15" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="K15" s="177">
         <v>20</v>
       </c>
-      <c r="L15" s="147">
+      <c r="L15" s="177">
         <v>40</v>
       </c>
-      <c r="M15" s="147">
+      <c r="M15" s="177">
         <v>10</v>
       </c>
-      <c r="N15" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="O15" s="147" t="s">
-        <v>128</v>
+      <c r="N15" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="O15" s="177" t="s">
+        <v>126</v>
       </c>
       <c r="P15">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="R15" s="149" t="s">
+      <c r="R15" s="181" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="16" spans="3:26" ht="15.95">
-      <c r="C16" s="146" t="s">
+    <row r="16" spans="3:26" ht="16">
+      <c r="C16" s="176" t="s">
         <v>213</v>
       </c>
-      <c r="D16" s="147">
+      <c r="D16" s="177">
         <v>20</v>
       </c>
-      <c r="E16" s="147">
+      <c r="E16" s="177">
         <v>5</v>
       </c>
-      <c r="F16" s="147">
+      <c r="F16" s="177">
         <v>10</v>
       </c>
-      <c r="G16" s="150">
+      <c r="G16" s="146">
         <v>20</v>
       </c>
-      <c r="H16" s="150">
+      <c r="H16" s="146">
         <v>5</v>
       </c>
-      <c r="I16" s="147">
+      <c r="I16" s="177">
         <v>25</v>
       </c>
-      <c r="J16" s="150">
+      <c r="J16" s="146">
         <v>5</v>
       </c>
-      <c r="K16" s="150">
+      <c r="K16" s="146">
         <v>20</v>
       </c>
-      <c r="L16" s="150">
+      <c r="L16" s="146">
         <v>20</v>
       </c>
-      <c r="M16" s="147">
+      <c r="M16" s="177">
         <v>5</v>
       </c>
-      <c r="N16" s="147">
+      <c r="N16" s="177">
         <v>10</v>
       </c>
-      <c r="O16" s="147"/>
+      <c r="O16" s="177"/>
       <c r="P16">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="3:16" ht="15.95">
-      <c r="C17" s="146" t="s">
+    <row r="17" spans="3:16" ht="16">
+      <c r="C17" s="176" t="s">
         <v>214</v>
       </c>
-      <c r="D17" s="147">
+      <c r="D17" s="177">
         <v>20</v>
       </c>
-      <c r="E17" s="147">
+      <c r="E17" s="177">
         <v>5</v>
       </c>
-      <c r="F17" s="147">
+      <c r="F17" s="177">
         <v>10</v>
       </c>
-      <c r="G17" s="150">
+      <c r="G17" s="146">
         <v>20</v>
       </c>
-      <c r="H17" s="150">
+      <c r="H17" s="146">
         <v>5</v>
       </c>
-      <c r="I17" s="147">
+      <c r="I17" s="177">
         <v>25</v>
       </c>
-      <c r="J17" s="150">
+      <c r="J17" s="146">
         <v>5</v>
       </c>
-      <c r="K17" s="150">
+      <c r="K17" s="146">
         <v>20</v>
       </c>
-      <c r="L17" s="150">
+      <c r="L17" s="146">
         <v>20</v>
       </c>
-      <c r="M17" s="147">
+      <c r="M17" s="177">
         <v>5</v>
       </c>
-      <c r="N17" s="147">
+      <c r="N17" s="177">
         <v>10</v>
       </c>
-      <c r="O17" s="147"/>
+      <c r="O17" s="177"/>
       <c r="P17">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="3:16" ht="15.95">
-      <c r="C18" s="146" t="s">
+    <row r="18" spans="3:16" ht="16">
+      <c r="C18" s="176" t="s">
         <v>215</v>
       </c>
-      <c r="D18" s="147">
+      <c r="D18" s="177">
         <v>20</v>
       </c>
-      <c r="E18" s="147">
+      <c r="E18" s="177">
         <v>5</v>
       </c>
-      <c r="F18" s="147">
+      <c r="F18" s="177">
         <v>10</v>
       </c>
-      <c r="G18" s="150">
+      <c r="G18" s="146">
         <v>20</v>
       </c>
-      <c r="H18" s="150">
+      <c r="H18" s="146">
         <v>5</v>
       </c>
-      <c r="I18" s="147">
+      <c r="I18" s="177">
         <v>25</v>
       </c>
-      <c r="J18" s="150">
+      <c r="J18" s="146">
         <v>5</v>
       </c>
-      <c r="K18" s="150">
+      <c r="K18" s="146">
         <v>20</v>
       </c>
-      <c r="L18" s="150">
+      <c r="L18" s="146">
         <v>20</v>
       </c>
-      <c r="M18" s="147">
+      <c r="M18" s="177">
         <v>5</v>
       </c>
-      <c r="N18" s="147">
+      <c r="N18" s="177">
         <v>10</v>
       </c>
-      <c r="O18" s="147"/>
+      <c r="O18" s="177"/>
       <c r="P18">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="3:16" ht="15.95">
-      <c r="C19" s="151" t="s">
+    <row r="19" spans="3:16" ht="16">
+      <c r="C19" s="182" t="s">
         <v>216</v>
       </c>
-      <c r="D19" s="151">
+      <c r="D19" s="182">
         <f t="shared" ref="D19:O19" si="1">SUM(D8:D18)</f>
         <v>150</v>
       </c>
-      <c r="E19" s="151">
+      <c r="E19" s="182">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="F19" s="151">
+      <c r="F19" s="182">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="G19" s="151">
+      <c r="G19" s="182">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="H19" s="151">
+      <c r="H19" s="182">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="I19" s="151">
+      <c r="I19" s="182">
         <f t="shared" si="1"/>
         <v>155</v>
       </c>
-      <c r="J19" s="151">
+      <c r="J19" s="182">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="K19" s="151">
+      <c r="K19" s="182">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="L19" s="151">
+      <c r="L19" s="182">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
-      <c r="M19" s="151">
+      <c r="M19" s="182">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="N19" s="151">
+      <c r="N19" s="182">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="O19" s="151">
+      <c r="O19" s="182">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
@@ -11177,14 +11191,14 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="3:16" ht="14.1">
+    <row r="22" spans="3:16" ht="14.5">
       <c r="D22" t="s">
         <v>220</v>
       </c>
       <c r="G22" t="s">
         <v>221</v>
       </c>
-      <c r="I22" s="152" t="s">
+      <c r="I22" s="147" t="s">
         <v>222</v>
       </c>
     </row>
@@ -11196,152 +11210,152 @@
         <v>224</v>
       </c>
     </row>
-    <row r="26" spans="3:16" ht="15.95">
-      <c r="C26" s="146" t="s">
+    <row r="26" spans="3:16" ht="16">
+      <c r="C26" s="176" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="273" t="s">
+      <c r="D26" s="267" t="s">
         <v>185</v>
       </c>
-      <c r="E26" s="274"/>
-      <c r="F26" s="274"/>
-      <c r="G26" s="274"/>
-      <c r="H26" s="274"/>
-      <c r="I26" s="274"/>
-      <c r="J26" s="274"/>
-      <c r="K26" s="274"/>
-      <c r="L26" s="274"/>
-      <c r="M26" s="274"/>
-      <c r="N26" s="274"/>
-      <c r="O26" s="275"/>
-    </row>
-    <row r="27" spans="3:16" ht="15.95">
-      <c r="C27" s="146" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="153" t="s">
+      <c r="E26" s="268"/>
+      <c r="F26" s="268"/>
+      <c r="G26" s="268"/>
+      <c r="H26" s="268"/>
+      <c r="I26" s="268"/>
+      <c r="J26" s="268"/>
+      <c r="K26" s="268"/>
+      <c r="L26" s="268"/>
+      <c r="M26" s="268"/>
+      <c r="N26" s="268"/>
+      <c r="O26" s="269"/>
+    </row>
+    <row r="27" spans="3:16" ht="16">
+      <c r="C27" s="176" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="183" t="s">
         <v>225</v>
       </c>
-      <c r="E27" s="147"/>
-      <c r="F27" s="147"/>
-      <c r="G27" s="148"/>
-      <c r="H27" s="153"/>
-      <c r="I27" s="153" t="s">
+      <c r="E27" s="177"/>
+      <c r="F27" s="177"/>
+      <c r="G27" s="178"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="183" t="s">
         <v>226</v>
       </c>
-      <c r="J27" s="147"/>
-      <c r="K27" s="147"/>
-      <c r="L27" s="147"/>
-      <c r="M27" s="147"/>
-      <c r="N27" s="147"/>
-      <c r="O27" s="147"/>
+      <c r="J27" s="177"/>
+      <c r="K27" s="177"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="177"/>
+      <c r="N27" s="177"/>
+      <c r="O27" s="177"/>
     </row>
     <row r="28" spans="3:16" ht="18">
-      <c r="C28" s="146" t="s">
+      <c r="C28" s="176" t="s">
         <v>197</v>
       </c>
-      <c r="D28" s="154" t="s">
+      <c r="D28" s="148" t="s">
         <v>227</v>
       </c>
-      <c r="I28" s="154" t="s">
+      <c r="I28" s="148" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="29" spans="3:16" ht="18">
-      <c r="C29" s="155" t="s">
+      <c r="C29" s="179" t="s">
         <v>199</v>
       </c>
-      <c r="D29" s="158" t="s">
+      <c r="D29" s="150" t="s">
         <v>229</v>
       </c>
-      <c r="E29" s="159"/>
-      <c r="F29" s="159"/>
-      <c r="G29" s="159"/>
-      <c r="H29" s="159"/>
-      <c r="I29" s="158" t="s">
+      <c r="E29" s="151"/>
+      <c r="F29" s="151"/>
+      <c r="G29" s="151"/>
+      <c r="H29" s="151"/>
+      <c r="I29" s="150" t="s">
         <v>230</v>
       </c>
-      <c r="J29" s="159"/>
-      <c r="K29" s="159"/>
+      <c r="J29" s="151"/>
+      <c r="K29" s="151"/>
     </row>
     <row r="30" spans="3:16" ht="18">
-      <c r="C30" s="146" t="s">
+      <c r="C30" s="176" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="154" t="s">
+      <c r="D30" s="148" t="s">
         <v>231</v>
       </c>
-      <c r="I30" s="154" t="s">
+      <c r="I30" s="148" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="31" spans="3:16" ht="18">
-      <c r="C31" s="146" t="s">
+      <c r="C31" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="D31" s="154" t="s">
+      <c r="D31" s="148" t="s">
         <v>233</v>
       </c>
-      <c r="I31" s="154" t="s">
+      <c r="I31" s="148" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="32" spans="3:16" ht="18">
-      <c r="C32" s="146" t="s">
+      <c r="C32" s="176" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="154" t="s">
+      <c r="D32" s="148" t="s">
         <v>235</v>
       </c>
-      <c r="I32" s="154" t="s">
+      <c r="I32" s="148" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="33" spans="3:18" ht="18">
-      <c r="C33" s="146" t="s">
+      <c r="C33" s="176" t="s">
         <v>207</v>
       </c>
-      <c r="D33" s="154" t="s">
+      <c r="D33" s="148" t="s">
         <v>237</v>
       </c>
-      <c r="I33" s="154" t="s">
+      <c r="I33" s="148" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="34" spans="3:18" ht="18">
-      <c r="C34" s="146" t="s">
+      <c r="C34" s="176" t="s">
         <v>209</v>
       </c>
-      <c r="D34" s="154" t="s">
+      <c r="D34" s="148" t="s">
         <v>239</v>
       </c>
-      <c r="I34" s="154" t="s">
+      <c r="I34" s="148" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="35" spans="3:18" ht="18">
-      <c r="C35" s="146" t="s">
+      <c r="C35" s="176" t="s">
         <v>211</v>
       </c>
-      <c r="D35" s="154" t="s">
+      <c r="D35" s="148" t="s">
         <v>241</v>
       </c>
-      <c r="I35" s="154" t="s">
+      <c r="I35" s="148" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="36" spans="3:18" ht="15.95">
-      <c r="C36" s="146" t="s">
+    <row r="36" spans="3:18" ht="16">
+      <c r="C36" s="176" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="37" spans="3:18" ht="15.95">
-      <c r="C37" s="146" t="s">
+    <row r="37" spans="3:18" ht="16">
+      <c r="C37" s="176" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="38" spans="3:18" ht="18">
-      <c r="R38" s="154"/>
+    <row r="38" spans="3:18" ht="17.5">
+      <c r="R38" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11358,13 +11372,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:T1000"/>
-  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" customWidth="1"/>
-    <col min="10" max="26" width="14.42578125" customWidth="1"/>
+    <col min="1" max="6" width="14.453125" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" customWidth="1"/>
+    <col min="8" max="8" width="14.453125" customWidth="1"/>
+    <col min="9" max="9" width="16.1796875" customWidth="1"/>
+    <col min="10" max="26" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" customHeight="1"/>
@@ -11372,11 +11386,11 @@
       <c r="A2" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="263" t="s">
+      <c r="B2" s="273" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="276"/>
-      <c r="D2" s="276"/>
+      <c r="C2" s="271"/>
+      <c r="D2" s="271"/>
       <c r="G2" s="2"/>
       <c r="H2" s="31" t="s">
         <v>244</v>
@@ -11438,11 +11452,11 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1">
-      <c r="B5" s="261" t="s">
+      <c r="B5" s="270" t="s">
         <v>250</v>
       </c>
-      <c r="C5" s="276"/>
-      <c r="D5" s="276"/>
+      <c r="C5" s="271"/>
+      <c r="D5" s="271"/>
       <c r="F5" s="1">
         <v>6.1</v>
       </c>
@@ -11525,11 +11539,11 @@
       <c r="T6" s="2"/>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1">
-      <c r="B7" s="261" t="s">
+      <c r="B7" s="270" t="s">
         <v>264</v>
       </c>
-      <c r="C7" s="276"/>
-      <c r="D7" s="276"/>
+      <c r="C7" s="271"/>
+      <c r="D7" s="271"/>
       <c r="F7" s="1">
         <v>6.2</v>
       </c>
@@ -11581,11 +11595,11 @@
       <c r="T7" s="3"/>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1">
-      <c r="B8" s="261" t="s">
+      <c r="B8" s="270" t="s">
         <v>272</v>
       </c>
-      <c r="C8" s="276"/>
-      <c r="D8" s="276"/>
+      <c r="C8" s="271"/>
+      <c r="D8" s="271"/>
       <c r="G8" s="2"/>
       <c r="H8" s="38" t="s">
         <v>258</v>
@@ -11649,9 +11663,9 @@
       <c r="M12" s="39"/>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1">
-      <c r="B13" s="262"/>
-      <c r="C13" s="276"/>
-      <c r="D13" s="276"/>
+      <c r="B13" s="272"/>
+      <c r="C13" s="271"/>
+      <c r="D13" s="271"/>
       <c r="G13" s="1"/>
       <c r="H13" s="2" t="s">
         <v>278</v>
@@ -11673,11 +11687,11 @@
       </c>
     </row>
     <row r="14" spans="1:20" ht="70.5" customHeight="1">
-      <c r="B14" s="261" t="s">
+      <c r="B14" s="270" t="s">
         <v>284</v>
       </c>
-      <c r="C14" s="276"/>
-      <c r="D14" s="276"/>
+      <c r="C14" s="271"/>
+      <c r="D14" s="271"/>
       <c r="F14" s="1">
         <v>3.1</v>
       </c>
@@ -11768,11 +11782,11 @@
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="2:19" ht="15.75" customHeight="1">
-      <c r="B18" s="261" t="s">
+      <c r="B18" s="270" t="s">
         <v>296</v>
       </c>
-      <c r="C18" s="276"/>
-      <c r="D18" s="276"/>
+      <c r="C18" s="271"/>
+      <c r="D18" s="271"/>
       <c r="F18" s="1">
         <v>3.2</v>
       </c>
@@ -11884,11 +11898,11 @@
       </c>
     </row>
     <row r="25" spans="2:19" ht="15.75" customHeight="1">
-      <c r="B25" s="262" t="s">
+      <c r="B25" s="272" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="276"/>
-      <c r="D25" s="276"/>
+      <c r="C25" s="271"/>
+      <c r="D25" s="271"/>
       <c r="G25" s="1" t="s">
         <v>309</v>
       </c>
@@ -12910,30 +12924,30 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="115.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" customWidth="1"/>
+    <col min="3" max="3" width="115.7265625" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" customWidth="1"/>
+    <col min="9" max="26" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A1" s="264" t="s">
+      <c r="A1" s="274" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="277"/>
-      <c r="C1" s="277"/>
-      <c r="D1" s="277"/>
-      <c r="E1" s="277"/>
-      <c r="F1" s="277"/>
-      <c r="G1" s="277"/>
-      <c r="H1" s="278"/>
+      <c r="B1" s="275"/>
+      <c r="C1" s="275"/>
+      <c r="D1" s="275"/>
+      <c r="E1" s="275"/>
+      <c r="F1" s="275"/>
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
@@ -12954,14 +12968,14 @@
       <c r="Z1" s="5"/>
     </row>
     <row r="2" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A2" s="279"/>
-      <c r="B2" s="276"/>
-      <c r="C2" s="276"/>
-      <c r="D2" s="276"/>
-      <c r="E2" s="276"/>
-      <c r="F2" s="276"/>
-      <c r="G2" s="276"/>
-      <c r="H2" s="280"/>
+      <c r="A2" s="277"/>
+      <c r="B2" s="271"/>
+      <c r="C2" s="271"/>
+      <c r="D2" s="271"/>
+      <c r="E2" s="271"/>
+      <c r="F2" s="271"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="278"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -12982,28 +12996,28 @@
       <c r="Z2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A3" s="265" t="s">
+      <c r="A3" s="279" t="s">
         <v>318</v>
       </c>
-      <c r="B3" s="276"/>
+      <c r="B3" s="271"/>
       <c r="C3" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="266" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="276"/>
-      <c r="F3" s="276"/>
-      <c r="G3" s="276"/>
-      <c r="H3" s="280"/>
+        <v>97</v>
+      </c>
+      <c r="D3" s="280" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="271"/>
+      <c r="F3" s="271"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="278"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="267" t="s">
+      <c r="K3" s="281" t="s">
         <v>319</v>
       </c>
-      <c r="L3" s="276"/>
-      <c r="M3" s="276"/>
-      <c r="N3" s="276"/>
+      <c r="L3" s="271"/>
+      <c r="M3" s="271"/>
+      <c r="N3" s="271"/>
       <c r="O3" s="43"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
@@ -13066,13 +13080,13 @@
         <v>321</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -13126,7 +13140,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>322</v>
@@ -13170,7 +13184,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>324</v>
@@ -13212,7 +13226,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>325</v>
@@ -13254,7 +13268,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>326</v>
@@ -13298,7 +13312,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>327</v>
@@ -41042,6 +41056,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5ff92c65-ed86-4457-baee-ccd535c9ea21">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6c8d291c-a5bf-4049-930d-38db8e991d8e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000BADAD4AA324BF48804EF76FD903323C" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4ea0feda506421460444ca95554a0aab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5ff92c65-ed86-4457-baee-ccd535c9ea21" xmlns:ns3="6c8d291c-a5bf-4049-930d-38db8e991d8e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0fc8cf7d0f5ee312899395875a30595e" ns2:_="" ns3:_="">
     <xsd:import namespace="5ff92c65-ed86-4457-baee-ccd535c9ea21"/>
@@ -41276,17 +41301,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5ff92c65-ed86-4457-baee-ccd535c9ea21">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6c8d291c-a5bf-4049-930d-38db8e991d8e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -41297,13 +41311,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F4F432-C7C0-460B-B718-CA5C7D43A268}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5072705-B970-4C6A-9B95-6E8AEA4192EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5ff92c65-ed86-4457-baee-ccd535c9ea21"/>
+    <ds:schemaRef ds:uri="6c8d291c-a5bf-4049-930d-38db8e991d8e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5072705-B970-4C6A-9B95-6E8AEA4192EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F4F432-C7C0-460B-B718-CA5C7D43A268}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5ff92c65-ed86-4457-baee-ccd535c9ea21"/>
+    <ds:schemaRef ds:uri="6c8d291c-a5bf-4049-930d-38db8e991d8e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1E7A10-6C2D-4580-A4D2-EC7B8465FD38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1E7A10-6C2D-4580-A4D2-EC7B8465FD38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Deliverables/Self Assessment Rubric - Y1B- 2024-25_ADSAI.xlsx
+++ b/Deliverables/Self Assessment Rubric - Y1B- 2024-25_ADSAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maksb\Documents\GitHub\2024-25b-fai1-adsai-MaksBurchard240894\Deliverables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB11FCF-8841-4AF7-93FD-49F60031DED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7DD12C-CC59-45F0-BEE1-AA60DE1224B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{DAAEC50E-5317-F24F-8628-0EA25586FBC3}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="331">
   <si>
     <t>Details</t>
   </si>
@@ -1137,6 +1137,9 @@
   </si>
   <si>
     <t>240894</t>
+  </si>
+  <si>
+    <t>This has been a block of ups and downs for me. Hopefully it ends on an up and not a down.</t>
   </si>
 </sst>
 </file>
@@ -4128,7 +4131,7 @@
         <v>329</v>
       </c>
       <c r="F3" s="189" t="s">
-        <v>5</v>
+        <v>330</v>
       </c>
       <c r="G3" s="190"/>
       <c r="H3" s="190"/>
@@ -4136,12 +4139,12 @@
       <c r="J3" s="190"/>
       <c r="K3" s="191"/>
       <c r="L3" s="192">
-        <v>0</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="M3" s="202"/>
       <c r="N3" s="198" t="str">
         <f>IF(L3&gt;=5.5,"PASS",IF(L3&gt;0,"FAIL","M/O"))</f>
-        <v>M/O</v>
+        <v>PASS</v>
       </c>
       <c r="O3" s="80"/>
     </row>
@@ -4655,8 +4658,8 @@
       </c>
       <c r="K23" s="225"/>
       <c r="L23" s="123">
-        <f>IF(F24="Yes",SUM(G24:K24),0)</f>
-        <v>8</v>
+        <f>IF(F16="Yes",SUM(G16:K16),0)</f>
+        <v>9</v>
       </c>
       <c r="M23" s="124" t="s">
         <v>34</v>
@@ -5256,7 +5259,7 @@
       </c>
       <c r="L39" s="67">
         <f>IF(F40="Yes",SUM(G40:K40),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M39" s="70" t="s">
         <v>34</v>
@@ -5288,19 +5291,19 @@
         <v>36</v>
       </c>
       <c r="G40" s="134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" s="134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" s="133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="67"/>
       <c r="M40" s="70"/>
@@ -5332,7 +5335,7 @@
       </c>
       <c r="L41" s="258">
         <f>SUM(L15:L40)</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="M41" s="259" t="s">
         <v>34</v>
